--- a/research/traditional_assets/database/data/greece/greece_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_construction_supplies.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.100696673382856</v>
+        <v>0.1005102407014137</v>
       </c>
       <c r="C2">
-        <v>98.68572541964659</v>
+        <v>97.88951669991242</v>
       </c>
       <c r="D2">
-        <v>89.57572541964659</v>
+        <v>89.75851669991242</v>
       </c>
       <c r="E2">
-        <v>-42.5</v>
+        <v>-41.521</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9790000000000001</v>
       </c>
       <c r="G2">
         <v>9.109999999999999</v>
@@ -1579,28 +1579,28 @@
         <v>19.825</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0492437</v>
       </c>
       <c r="N2">
-        <v>19.825</v>
+        <v>19.7757563</v>
       </c>
       <c r="O2">
-        <v>4.361499999999999</v>
+        <v>4.350666385999999</v>
       </c>
       <c r="P2">
-        <v>15.4635</v>
+        <v>15.425089914</v>
       </c>
       <c r="Q2">
-        <v>16.2635</v>
+        <v>16.225089914</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.100696673382856</v>
+        <v>0.1011291926276906</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7211248600721448</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>402.5895698332984</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1005102407014137</v>
+        <v>0.1003238080199714</v>
       </c>
       <c r="C3">
-        <v>97.88951669991242</v>
+        <v>97.09405552588674</v>
       </c>
       <c r="D3">
-        <v>89.75851669991242</v>
+        <v>89.94205552588674</v>
       </c>
       <c r="E3">
-        <v>-41.521</v>
+        <v>-40.542</v>
       </c>
       <c r="F3">
-        <v>0.9790000000000001</v>
+        <v>1.958</v>
       </c>
       <c r="G3">
         <v>9.109999999999999</v>
@@ -1661,28 +1661,28 @@
         <v>19.825</v>
       </c>
       <c r="M3">
-        <v>0.0492437</v>
+        <v>0.0984874</v>
       </c>
       <c r="N3">
-        <v>19.7757563</v>
+        <v>19.7265126</v>
       </c>
       <c r="O3">
-        <v>4.350666385999999</v>
+        <v>4.339832772</v>
       </c>
       <c r="P3">
-        <v>15.425089914</v>
+        <v>15.386679828</v>
       </c>
       <c r="Q3">
-        <v>16.225089914</v>
+        <v>16.186679828</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1011291926276906</v>
+        <v>0.1015705387958892</v>
       </c>
       <c r="T3">
-        <v>0.7211248600721448</v>
+        <v>0.7268770801691774</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>402.5895698332984</v>
+        <v>201.2947849166492</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1003238080199714</v>
+        <v>0.1001373753385291</v>
       </c>
       <c r="C4">
-        <v>97.09405552588674</v>
+        <v>96.29934649272535</v>
       </c>
       <c r="D4">
-        <v>89.94205552588674</v>
+        <v>90.12634649272535</v>
       </c>
       <c r="E4">
-        <v>-40.542</v>
+        <v>-39.563</v>
       </c>
       <c r="F4">
-        <v>1.958</v>
+        <v>2.937</v>
       </c>
       <c r="G4">
         <v>9.109999999999999</v>
@@ -1743,28 +1743,28 @@
         <v>19.825</v>
       </c>
       <c r="M4">
-        <v>0.0984874</v>
+        <v>0.1477311</v>
       </c>
       <c r="N4">
-        <v>19.7265126</v>
+        <v>19.6772689</v>
       </c>
       <c r="O4">
-        <v>4.339832772</v>
+        <v>4.328999157999999</v>
       </c>
       <c r="P4">
-        <v>15.386679828</v>
+        <v>15.348269742</v>
       </c>
       <c r="Q4">
-        <v>16.186679828</v>
+        <v>16.148269742</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1015705387958892</v>
+        <v>0.1020209848850816</v>
       </c>
       <c r="T4">
-        <v>0.7268770801691774</v>
+        <v>0.7327479027424375</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>201.2947849166492</v>
+        <v>134.1965232777661</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1001373753385291</v>
+        <v>0.09995094265708683</v>
       </c>
       <c r="C5">
-        <v>96.29934649272535</v>
+        <v>95.50539423332333</v>
       </c>
       <c r="D5">
-        <v>90.12634649272535</v>
+        <v>90.31139423332333</v>
       </c>
       <c r="E5">
-        <v>-39.563</v>
+        <v>-38.584</v>
       </c>
       <c r="F5">
-        <v>2.937</v>
+        <v>3.916</v>
       </c>
       <c r="G5">
         <v>9.109999999999999</v>
@@ -1825,28 +1825,28 @@
         <v>19.825</v>
       </c>
       <c r="M5">
-        <v>0.1477311</v>
+        <v>0.1969748</v>
       </c>
       <c r="N5">
-        <v>19.6772689</v>
+        <v>19.6280252</v>
       </c>
       <c r="O5">
-        <v>4.328999157999999</v>
+        <v>4.318165544</v>
       </c>
       <c r="P5">
-        <v>15.348269742</v>
+        <v>15.309859656</v>
       </c>
       <c r="Q5">
-        <v>16.148269742</v>
+        <v>16.109859656</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1020209848850816</v>
+        <v>0.1024808152677988</v>
       </c>
       <c r="T5">
-        <v>0.7327479027424375</v>
+        <v>0.7387410341193071</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>134.1965232777661</v>
+        <v>100.6473924583246</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09995094265708683</v>
+        <v>0.09976450997564454</v>
       </c>
       <c r="C6">
-        <v>95.50539423332333</v>
+        <v>94.7122034187031</v>
       </c>
       <c r="D6">
-        <v>90.31139423332333</v>
+        <v>90.49720341870309</v>
       </c>
       <c r="E6">
-        <v>-38.584</v>
+        <v>-37.605</v>
       </c>
       <c r="F6">
-        <v>3.916</v>
+        <v>4.895</v>
       </c>
       <c r="G6">
         <v>9.109999999999999</v>
@@ -1907,28 +1907,28 @@
         <v>19.825</v>
       </c>
       <c r="M6">
-        <v>0.1969748</v>
+        <v>0.2462185</v>
       </c>
       <c r="N6">
-        <v>19.6280252</v>
+        <v>19.5787815</v>
       </c>
       <c r="O6">
-        <v>4.318165544</v>
+        <v>4.307331929999999</v>
       </c>
       <c r="P6">
-        <v>15.309859656</v>
+        <v>15.27144957</v>
       </c>
       <c r="Q6">
-        <v>16.109859656</v>
+        <v>16.07144957</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1024808152677988</v>
+        <v>0.1029503262901522</v>
       </c>
       <c r="T6">
-        <v>0.7387410341193071</v>
+        <v>0.7448603366830583</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>100.6473924583246</v>
+        <v>80.51791396665969</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09976450997564454</v>
+        <v>0.09957807729420226</v>
       </c>
       <c r="C7">
-        <v>94.7122034187031</v>
+        <v>93.91977875840746</v>
       </c>
       <c r="D7">
-        <v>90.49720341870309</v>
+        <v>90.68377875840746</v>
       </c>
       <c r="E7">
-        <v>-37.605</v>
+        <v>-36.626</v>
       </c>
       <c r="F7">
-        <v>4.895</v>
+        <v>5.874000000000001</v>
       </c>
       <c r="G7">
         <v>9.109999999999999</v>
@@ -1989,28 +1989,28 @@
         <v>19.825</v>
       </c>
       <c r="M7">
-        <v>0.2462185</v>
+        <v>0.2954622</v>
       </c>
       <c r="N7">
-        <v>19.5787815</v>
+        <v>19.5295378</v>
       </c>
       <c r="O7">
-        <v>4.307331929999999</v>
+        <v>4.296498316</v>
       </c>
       <c r="P7">
-        <v>15.27144957</v>
+        <v>15.233039484</v>
       </c>
       <c r="Q7">
-        <v>16.07144957</v>
+        <v>16.033039484</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1029503262901522</v>
+        <v>0.1034298269087258</v>
       </c>
       <c r="T7">
-        <v>0.7448603366830583</v>
+        <v>0.7511098371736976</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>80.51791396665969</v>
+        <v>67.09826163888307</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09957807729420226</v>
+        <v>0.09939164461275998</v>
       </c>
       <c r="C8">
-        <v>93.91977875840746</v>
+        <v>93.12812500089761</v>
       </c>
       <c r="D8">
-        <v>90.68377875840746</v>
+        <v>90.87112500089761</v>
       </c>
       <c r="E8">
-        <v>-36.626</v>
+        <v>-35.647</v>
       </c>
       <c r="F8">
-        <v>5.874000000000001</v>
+        <v>6.853</v>
       </c>
       <c r="G8">
         <v>9.109999999999999</v>
@@ -2071,28 +2071,28 @@
         <v>19.825</v>
       </c>
       <c r="M8">
-        <v>0.2954622</v>
+        <v>0.3447059</v>
       </c>
       <c r="N8">
-        <v>19.5295378</v>
+        <v>19.4802941</v>
       </c>
       <c r="O8">
-        <v>4.296498316</v>
+        <v>4.285664702</v>
       </c>
       <c r="P8">
-        <v>15.233039484</v>
+        <v>15.194629398</v>
       </c>
       <c r="Q8">
-        <v>16.033039484</v>
+        <v>15.994629398</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1034298269087258</v>
+        <v>0.1039196393685591</v>
       </c>
       <c r="T8">
-        <v>0.7511098371736976</v>
+        <v>0.7574937355243507</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>67.09826163888307</v>
+        <v>57.51279569047121</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09939164461276</v>
+        <v>0.0992052119313177</v>
       </c>
       <c r="C9">
-        <v>93.1281250008976</v>
+        <v>92.33724693395587</v>
       </c>
       <c r="D9">
-        <v>90.87112500089759</v>
+        <v>91.05924693395586</v>
       </c>
       <c r="E9">
-        <v>-35.647</v>
+        <v>-34.668</v>
       </c>
       <c r="F9">
-        <v>6.853000000000001</v>
+        <v>7.832000000000001</v>
       </c>
       <c r="G9">
         <v>9.109999999999999</v>
@@ -2153,28 +2153,28 @@
         <v>19.825</v>
       </c>
       <c r="M9">
-        <v>0.3447059</v>
+        <v>0.3939496</v>
       </c>
       <c r="N9">
-        <v>19.4802941</v>
+        <v>19.4310504</v>
       </c>
       <c r="O9">
-        <v>4.285664702</v>
+        <v>4.274831088</v>
       </c>
       <c r="P9">
-        <v>15.194629398</v>
+        <v>15.156219312</v>
       </c>
       <c r="Q9">
-        <v>15.994629398</v>
+        <v>15.956219312</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1039196393685591</v>
+        <v>0.1044200999253453</v>
       </c>
       <c r="T9">
-        <v>0.757493735524351</v>
+        <v>0.7640164142739313</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>57.5127956904712</v>
+        <v>50.32369622916231</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0992052119313177</v>
+        <v>0.09901877924987543</v>
       </c>
       <c r="C10">
-        <v>92.33724693395587</v>
+        <v>91.54714938509358</v>
       </c>
       <c r="D10">
-        <v>91.05924693395586</v>
+        <v>91.24814938509358</v>
       </c>
       <c r="E10">
-        <v>-34.668</v>
+        <v>-33.689</v>
       </c>
       <c r="F10">
-        <v>7.832000000000001</v>
+        <v>8.811</v>
       </c>
       <c r="G10">
         <v>9.109999999999999</v>
@@ -2235,28 +2235,28 @@
         <v>19.825</v>
       </c>
       <c r="M10">
-        <v>0.3939496</v>
+        <v>0.4431933</v>
       </c>
       <c r="N10">
-        <v>19.4310504</v>
+        <v>19.3818067</v>
       </c>
       <c r="O10">
-        <v>4.274831088</v>
+        <v>4.263997474</v>
       </c>
       <c r="P10">
-        <v>15.156219312</v>
+        <v>15.117809226</v>
       </c>
       <c r="Q10">
-        <v>15.956219312</v>
+        <v>15.917809226</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1044200999253453</v>
+        <v>0.1049315596152477</v>
       </c>
       <c r="T10">
-        <v>0.7640164142739313</v>
+        <v>0.7706824486004256</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>50.32369622916231</v>
+        <v>44.73217442592205</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09901877924987543</v>
+        <v>0.09883234656843314</v>
       </c>
       <c r="C11">
-        <v>91.54714938509358</v>
+        <v>90.75783722196414</v>
       </c>
       <c r="D11">
-        <v>91.24814938509358</v>
+        <v>91.43783722196414</v>
       </c>
       <c r="E11">
-        <v>-33.689</v>
+        <v>-32.71</v>
       </c>
       <c r="F11">
-        <v>8.811</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G11">
         <v>9.109999999999999</v>
@@ -2317,28 +2317,28 @@
         <v>19.825</v>
       </c>
       <c r="M11">
-        <v>0.4431933</v>
+        <v>0.492437</v>
       </c>
       <c r="N11">
-        <v>19.3818067</v>
+        <v>19.332563</v>
       </c>
       <c r="O11">
-        <v>4.263997474</v>
+        <v>4.25316386</v>
       </c>
       <c r="P11">
-        <v>15.117809226</v>
+        <v>15.07939914</v>
       </c>
       <c r="Q11">
-        <v>15.917809226</v>
+        <v>15.87939914</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1049315596152477</v>
+        <v>0.1054543850760368</v>
       </c>
       <c r="T11">
-        <v>0.7706824486004256</v>
+        <v>0.7774966170230642</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>44.73217442592205</v>
+        <v>40.25895698332985</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09883234656843314</v>
+        <v>0.09864591388699086</v>
       </c>
       <c r="C12">
-        <v>90.75783722196414</v>
+        <v>89.96931535278088</v>
       </c>
       <c r="D12">
-        <v>91.43783722196414</v>
+        <v>91.62831535278089</v>
       </c>
       <c r="E12">
-        <v>-32.71</v>
+        <v>-31.731</v>
       </c>
       <c r="F12">
-        <v>9.790000000000001</v>
+        <v>10.769</v>
       </c>
       <c r="G12">
         <v>9.109999999999999</v>
@@ -2399,28 +2399,28 @@
         <v>19.825</v>
       </c>
       <c r="M12">
-        <v>0.492437</v>
+        <v>0.5416807</v>
       </c>
       <c r="N12">
-        <v>19.332563</v>
+        <v>19.2833193</v>
       </c>
       <c r="O12">
-        <v>4.25316386</v>
+        <v>4.242330246</v>
       </c>
       <c r="P12">
-        <v>15.07939914</v>
+        <v>15.040989054</v>
       </c>
       <c r="Q12">
-        <v>15.87939914</v>
+        <v>15.840989054</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1054543850760368</v>
+        <v>0.1059889594235852</v>
       </c>
       <c r="T12">
-        <v>0.7774966170230642</v>
+        <v>0.7844639128259868</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>40.25895698332985</v>
+        <v>36.59905180302713</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09864591388699086</v>
+        <v>0.09845948120554858</v>
       </c>
       <c r="C13">
-        <v>89.96931535278088</v>
+        <v>89.18158872674069</v>
       </c>
       <c r="D13">
-        <v>91.62831535278089</v>
+        <v>91.81958872674069</v>
       </c>
       <c r="E13">
-        <v>-31.731</v>
+        <v>-30.752</v>
       </c>
       <c r="F13">
-        <v>10.769</v>
+        <v>11.748</v>
       </c>
       <c r="G13">
         <v>9.109999999999999</v>
@@ -2481,28 +2481,28 @@
         <v>19.825</v>
       </c>
       <c r="M13">
-        <v>0.5416807</v>
+        <v>0.5909244</v>
       </c>
       <c r="N13">
-        <v>19.2833193</v>
+        <v>19.2340756</v>
       </c>
       <c r="O13">
-        <v>4.242330246</v>
+        <v>4.231496632</v>
       </c>
       <c r="P13">
-        <v>15.040989054</v>
+        <v>15.002578968</v>
       </c>
       <c r="Q13">
-        <v>15.840989054</v>
+        <v>15.802578968</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1059889594235852</v>
+        <v>0.1065356831881234</v>
       </c>
       <c r="T13">
-        <v>0.7844639128259868</v>
+        <v>0.7915895562607941</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.59905180302713</v>
+        <v>33.54913081944154</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09845948120554858</v>
+        <v>0.09827304852410629</v>
       </c>
       <c r="C14">
-        <v>89.18158872674069</v>
+        <v>88.39466233445245</v>
       </c>
       <c r="D14">
-        <v>91.81958872674069</v>
+        <v>92.01166233445245</v>
       </c>
       <c r="E14">
-        <v>-30.752</v>
+        <v>-29.773</v>
       </c>
       <c r="F14">
-        <v>11.748</v>
+        <v>12.727</v>
       </c>
       <c r="G14">
         <v>9.109999999999999</v>
@@ -2563,28 +2563,28 @@
         <v>19.825</v>
       </c>
       <c r="M14">
-        <v>0.5909244</v>
+        <v>0.6401681</v>
       </c>
       <c r="N14">
-        <v>19.2340756</v>
+        <v>19.1848319</v>
       </c>
       <c r="O14">
-        <v>4.231496632</v>
+        <v>4.220663018</v>
       </c>
       <c r="P14">
-        <v>15.002578968</v>
+        <v>14.964168882</v>
       </c>
       <c r="Q14">
-        <v>15.802578968</v>
+        <v>15.764168882</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1065356831881234</v>
+        <v>0.1070949753150647</v>
       </c>
       <c r="T14">
-        <v>0.7915895562607941</v>
+        <v>0.7988790075906542</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.54913081944154</v>
+        <v>30.96842844871527</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09827304852410629</v>
+        <v>0.09808661584266401</v>
       </c>
       <c r="C15">
-        <v>88.39466233445245</v>
+        <v>87.60854120837125</v>
       </c>
       <c r="D15">
-        <v>92.01166233445245</v>
+        <v>92.20454120837125</v>
       </c>
       <c r="E15">
-        <v>-29.773</v>
+        <v>-28.794</v>
       </c>
       <c r="F15">
-        <v>12.727</v>
+        <v>13.706</v>
       </c>
       <c r="G15">
         <v>9.109999999999999</v>
@@ -2645,28 +2645,28 @@
         <v>19.825</v>
       </c>
       <c r="M15">
-        <v>0.6401681</v>
+        <v>0.6894118</v>
       </c>
       <c r="N15">
-        <v>19.1848319</v>
+        <v>19.1355882</v>
       </c>
       <c r="O15">
-        <v>4.220663018</v>
+        <v>4.209829404000001</v>
       </c>
       <c r="P15">
-        <v>14.964168882</v>
+        <v>14.925758796</v>
       </c>
       <c r="Q15">
-        <v>15.764168882</v>
+        <v>15.725758796</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1070949753150647</v>
+        <v>0.1076672742356558</v>
       </c>
       <c r="T15">
-        <v>0.7988790075906542</v>
+        <v>0.8063379810444647</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.96842844871527</v>
+        <v>28.7563978452356</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09808661584266401</v>
+        <v>0.09790018316122172</v>
       </c>
       <c r="C16">
-        <v>87.60854120837125</v>
+        <v>86.82323042323777</v>
       </c>
       <c r="D16">
-        <v>92.20454120837125</v>
+        <v>92.39823042323778</v>
       </c>
       <c r="E16">
-        <v>-28.794</v>
+        <v>-27.815</v>
       </c>
       <c r="F16">
-        <v>13.706</v>
+        <v>14.685</v>
       </c>
       <c r="G16">
         <v>9.109999999999999</v>
@@ -2727,28 +2727,28 @@
         <v>19.825</v>
       </c>
       <c r="M16">
-        <v>0.6894118</v>
+        <v>0.7386555000000001</v>
       </c>
       <c r="N16">
-        <v>19.1355882</v>
+        <v>19.0863445</v>
       </c>
       <c r="O16">
-        <v>4.209829404000001</v>
+        <v>4.19899579</v>
       </c>
       <c r="P16">
-        <v>14.925758796</v>
+        <v>14.88734871</v>
       </c>
       <c r="Q16">
-        <v>15.725758796</v>
+        <v>15.68734871</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1076672742356558</v>
+        <v>0.108253039013202</v>
       </c>
       <c r="T16">
-        <v>0.8063379810444647</v>
+        <v>0.813972459756012</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.7563978452356</v>
+        <v>26.83930465555322</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09790018316122172</v>
+        <v>0.09771375047977943</v>
       </c>
       <c r="C17">
-        <v>86.82323042323777</v>
+        <v>86.03873509652348</v>
       </c>
       <c r="D17">
-        <v>92.39823042323778</v>
+        <v>92.59273509652348</v>
       </c>
       <c r="E17">
-        <v>-27.815</v>
+        <v>-26.836</v>
       </c>
       <c r="F17">
-        <v>14.685</v>
+        <v>15.664</v>
       </c>
       <c r="G17">
         <v>9.109999999999999</v>
@@ -2809,28 +2809,28 @@
         <v>19.825</v>
       </c>
       <c r="M17">
-        <v>0.7386555</v>
+        <v>0.7878992</v>
       </c>
       <c r="N17">
-        <v>19.0863445</v>
+        <v>19.0371008</v>
       </c>
       <c r="O17">
-        <v>4.19899579</v>
+        <v>4.188162176</v>
       </c>
       <c r="P17">
-        <v>14.88734871</v>
+        <v>14.848938624</v>
       </c>
       <c r="Q17">
-        <v>15.68734871</v>
+        <v>15.648938624</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.108253039013202</v>
+        <v>0.108852750571166</v>
       </c>
       <c r="T17">
-        <v>0.813972459756012</v>
+        <v>0.8217887117702151</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.83930465555323</v>
+        <v>25.16184811458115</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09771375047977943</v>
+        <v>0.09752731779833715</v>
       </c>
       <c r="C18">
-        <v>86.03873509652348</v>
+        <v>85.25506038888115</v>
       </c>
       <c r="D18">
-        <v>92.59273509652348</v>
+        <v>92.78806038888115</v>
       </c>
       <c r="E18">
-        <v>-26.836</v>
+        <v>-25.857</v>
       </c>
       <c r="F18">
-        <v>15.664</v>
+        <v>16.643</v>
       </c>
       <c r="G18">
         <v>9.109999999999999</v>
@@ -2891,28 +2891,28 @@
         <v>19.825</v>
       </c>
       <c r="M18">
-        <v>0.7878992</v>
+        <v>0.8371429</v>
       </c>
       <c r="N18">
-        <v>19.0371008</v>
+        <v>18.9878571</v>
       </c>
       <c r="O18">
-        <v>4.188162176</v>
+        <v>4.177328562</v>
       </c>
       <c r="P18">
-        <v>14.848938624</v>
+        <v>14.810528538</v>
       </c>
       <c r="Q18">
-        <v>15.648938624</v>
+        <v>15.610528538</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.108852750571166</v>
+        <v>0.1094669130100448</v>
       </c>
       <c r="T18">
-        <v>0.8217887117702151</v>
+        <v>0.8297933072064472</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.16184811458115</v>
+        <v>23.68173940195873</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09752731779833715</v>
+        <v>0.09734088511689488</v>
       </c>
       <c r="C19">
-        <v>85.25506038888115</v>
+        <v>84.47221150460149</v>
       </c>
       <c r="D19">
-        <v>92.78806038888115</v>
+        <v>92.98421150460149</v>
       </c>
       <c r="E19">
-        <v>-25.857</v>
+        <v>-24.878</v>
       </c>
       <c r="F19">
-        <v>16.643</v>
+        <v>17.622</v>
       </c>
       <c r="G19">
         <v>9.109999999999999</v>
@@ -2973,28 +2973,28 @@
         <v>19.825</v>
       </c>
       <c r="M19">
-        <v>0.8371429</v>
+        <v>0.8863866000000001</v>
       </c>
       <c r="N19">
-        <v>18.9878571</v>
+        <v>18.9386134</v>
       </c>
       <c r="O19">
-        <v>4.177328562</v>
+        <v>4.166494948</v>
       </c>
       <c r="P19">
-        <v>14.810528538</v>
+        <v>14.772118452</v>
       </c>
       <c r="Q19">
-        <v>15.610528538</v>
+        <v>15.572118452</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1094669130100448</v>
+        <v>0.1100960550206035</v>
       </c>
       <c r="T19">
-        <v>0.8297933072064472</v>
+        <v>0.8379931366777094</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.68173940195873</v>
+        <v>22.36608721296102</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09734088511689487</v>
+        <v>0.09715445243545259</v>
       </c>
       <c r="C20">
-        <v>84.47221150460152</v>
+        <v>83.69019369207534</v>
       </c>
       <c r="D20">
-        <v>92.98421150460152</v>
+        <v>93.18119369207534</v>
       </c>
       <c r="E20">
-        <v>-24.878</v>
+        <v>-23.899</v>
       </c>
       <c r="F20">
-        <v>17.622</v>
+        <v>18.601</v>
       </c>
       <c r="G20">
         <v>9.109999999999999</v>
@@ -3055,28 +3055,28 @@
         <v>19.825</v>
       </c>
       <c r="M20">
-        <v>0.8863865999999999</v>
+        <v>0.9356303000000001</v>
       </c>
       <c r="N20">
-        <v>18.9386134</v>
+        <v>18.8893697</v>
       </c>
       <c r="O20">
-        <v>4.166494948</v>
+        <v>4.155661334</v>
       </c>
       <c r="P20">
-        <v>14.772118452</v>
+        <v>14.733708366</v>
       </c>
       <c r="Q20">
-        <v>15.572118452</v>
+        <v>15.533708366</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1100960550206035</v>
+        <v>0.1107407314017933</v>
       </c>
       <c r="T20">
-        <v>0.8379931366777092</v>
+        <v>0.8463954310741878</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.36608721296103</v>
+        <v>21.18892472806834</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09715445243545259</v>
+        <v>0.09696801975401032</v>
       </c>
       <c r="C21">
-        <v>83.69019369207534</v>
+        <v>82.9090122442616</v>
       </c>
       <c r="D21">
-        <v>93.18119369207534</v>
+        <v>93.3790122442616</v>
       </c>
       <c r="E21">
-        <v>-23.899</v>
+        <v>-22.92</v>
       </c>
       <c r="F21">
-        <v>18.601</v>
+        <v>19.58</v>
       </c>
       <c r="G21">
         <v>9.109999999999999</v>
@@ -3137,28 +3137,28 @@
         <v>19.825</v>
       </c>
       <c r="M21">
-        <v>0.9356303000000001</v>
+        <v>0.984874</v>
       </c>
       <c r="N21">
-        <v>18.8893697</v>
+        <v>18.840126</v>
       </c>
       <c r="O21">
-        <v>4.155661334</v>
+        <v>4.144827719999999</v>
       </c>
       <c r="P21">
-        <v>14.733708366</v>
+        <v>14.69529828</v>
       </c>
       <c r="Q21">
-        <v>15.533708366</v>
+        <v>15.49529828</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1107407314017933</v>
+        <v>0.1114015246925129</v>
       </c>
       <c r="T21">
-        <v>0.8463954310741878</v>
+        <v>0.8550077828305782</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.18892472806834</v>
+        <v>20.12947849166492</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09696801975401032</v>
+        <v>0.09678158707256804</v>
       </c>
       <c r="C22">
-        <v>82.9090122442616</v>
+        <v>82.1286724991615</v>
       </c>
       <c r="D22">
-        <v>93.3790122442616</v>
+        <v>93.57767249916149</v>
       </c>
       <c r="E22">
-        <v>-22.92</v>
+        <v>-21.941</v>
       </c>
       <c r="F22">
-        <v>19.58</v>
+        <v>20.559</v>
       </c>
       <c r="G22">
         <v>9.109999999999999</v>
@@ -3219,28 +3219,28 @@
         <v>19.825</v>
       </c>
       <c r="M22">
-        <v>0.984874</v>
+        <v>1.0341177</v>
       </c>
       <c r="N22">
-        <v>18.840126</v>
+        <v>18.7908823</v>
       </c>
       <c r="O22">
-        <v>4.144827719999999</v>
+        <v>4.133994106</v>
       </c>
       <c r="P22">
-        <v>14.69529828</v>
+        <v>14.656888194</v>
       </c>
       <c r="Q22">
-        <v>15.49529828</v>
+        <v>15.456888194</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1114015246925129</v>
+        <v>0.1120790469273013</v>
       </c>
       <c r="T22">
-        <v>0.8550077828305782</v>
+        <v>0.8638381688086495</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.12947849166492</v>
+        <v>19.17093189682373</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09678158707256801</v>
+        <v>0.09659515439112575</v>
       </c>
       <c r="C23">
-        <v>82.12867249916151</v>
+        <v>81.34917984029866</v>
       </c>
       <c r="D23">
-        <v>93.57767249916151</v>
+        <v>93.77717984029866</v>
       </c>
       <c r="E23">
-        <v>-21.941</v>
+        <v>-20.962</v>
       </c>
       <c r="F23">
-        <v>20.559</v>
+        <v>21.538</v>
       </c>
       <c r="G23">
         <v>9.109999999999999</v>
@@ -3301,28 +3301,28 @@
         <v>19.825</v>
       </c>
       <c r="M23">
-        <v>1.0341177</v>
+        <v>1.0833614</v>
       </c>
       <c r="N23">
-        <v>18.7908823</v>
+        <v>18.7416386</v>
       </c>
       <c r="O23">
-        <v>4.133994106</v>
+        <v>4.123160491999999</v>
       </c>
       <c r="P23">
-        <v>14.656888194</v>
+        <v>14.618478108</v>
       </c>
       <c r="Q23">
-        <v>15.456888194</v>
+        <v>15.418478108</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1120790469273013</v>
+        <v>0.1127739415270843</v>
       </c>
       <c r="T23">
-        <v>0.8638381688086494</v>
+        <v>0.8728949749400046</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.17093189682374</v>
+        <v>18.29952590151357</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09659515439112575</v>
+        <v>0.09640872170968345</v>
       </c>
       <c r="C24">
-        <v>81.34917984029866</v>
+        <v>80.57053969720545</v>
       </c>
       <c r="D24">
-        <v>93.77717984029866</v>
+        <v>93.97753969720544</v>
       </c>
       <c r="E24">
-        <v>-20.962</v>
+        <v>-19.983</v>
       </c>
       <c r="F24">
-        <v>21.538</v>
+        <v>22.517</v>
       </c>
       <c r="G24">
         <v>9.109999999999999</v>
@@ -3383,28 +3383,28 @@
         <v>19.825</v>
       </c>
       <c r="M24">
-        <v>1.0833614</v>
+        <v>1.1326051</v>
       </c>
       <c r="N24">
-        <v>18.7416386</v>
+        <v>18.6923949</v>
       </c>
       <c r="O24">
-        <v>4.123160491999999</v>
+        <v>4.112326878</v>
       </c>
       <c r="P24">
-        <v>14.618478108</v>
+        <v>14.580068022</v>
       </c>
       <c r="Q24">
-        <v>15.418478108</v>
+        <v>15.380068022</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1127739415270843</v>
+        <v>0.1134868853372512</v>
       </c>
       <c r="T24">
-        <v>0.8728949749400046</v>
+        <v>0.8821870227890573</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.29952590151357</v>
+        <v>17.50389434057819</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09640872170968345</v>
+        <v>0.09622228902824118</v>
       </c>
       <c r="C25">
-        <v>80.57053969720545</v>
+        <v>79.79275754591546</v>
       </c>
       <c r="D25">
-        <v>93.97753969720544</v>
+        <v>94.17875754591547</v>
       </c>
       <c r="E25">
-        <v>-19.983</v>
+        <v>-19.004</v>
       </c>
       <c r="F25">
-        <v>22.517</v>
+        <v>23.496</v>
       </c>
       <c r="G25">
         <v>9.109999999999999</v>
@@ -3465,28 +3465,28 @@
         <v>19.825</v>
       </c>
       <c r="M25">
-        <v>1.1326051</v>
+        <v>1.1818488</v>
       </c>
       <c r="N25">
-        <v>18.6923949</v>
+        <v>18.6431512</v>
       </c>
       <c r="O25">
-        <v>4.112326878</v>
+        <v>4.101493263999999</v>
       </c>
       <c r="P25">
-        <v>14.580068022</v>
+        <v>14.541657936</v>
       </c>
       <c r="Q25">
-        <v>15.380068022</v>
+        <v>15.341657936</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1134868853372512</v>
+        <v>0.1142185908266331</v>
       </c>
       <c r="T25">
-        <v>0.8821870227890573</v>
+        <v>0.8917235982130849</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.50389434057819</v>
+        <v>16.77456540972077</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09622228902824118</v>
+        <v>0.09603585634679888</v>
       </c>
       <c r="C26">
-        <v>79.79275754591546</v>
+        <v>79.01583890946253</v>
       </c>
       <c r="D26">
-        <v>94.17875754591547</v>
+        <v>94.38083890946254</v>
       </c>
       <c r="E26">
-        <v>-19.004</v>
+        <v>-18.025</v>
       </c>
       <c r="F26">
-        <v>23.496</v>
+        <v>24.475</v>
       </c>
       <c r="G26">
         <v>9.109999999999999</v>
@@ -3547,28 +3547,28 @@
         <v>19.825</v>
       </c>
       <c r="M26">
-        <v>1.1818488</v>
+        <v>1.2310925</v>
       </c>
       <c r="N26">
-        <v>18.6431512</v>
+        <v>18.5939075</v>
       </c>
       <c r="O26">
-        <v>4.101493263999999</v>
+        <v>4.09065965</v>
       </c>
       <c r="P26">
-        <v>14.541657936</v>
+        <v>14.50324785</v>
       </c>
       <c r="Q26">
-        <v>15.341657936</v>
+        <v>15.30324785</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1142185908266331</v>
+        <v>0.1149698084623985</v>
       </c>
       <c r="T26">
-        <v>0.8917235982130849</v>
+        <v>0.9015144823150867</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.77456540972077</v>
+        <v>16.10358279333194</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09603585634679888</v>
+        <v>0.09584942366535662</v>
       </c>
       <c r="C27">
-        <v>79.01583890946253</v>
+        <v>78.23978935838591</v>
       </c>
       <c r="D27">
-        <v>94.38083890946254</v>
+        <v>94.58378935838591</v>
       </c>
       <c r="E27">
-        <v>-18.025</v>
+        <v>-17.046</v>
       </c>
       <c r="F27">
-        <v>24.475</v>
+        <v>25.454</v>
       </c>
       <c r="G27">
         <v>9.109999999999999</v>
@@ -3629,28 +3629,28 @@
         <v>19.825</v>
       </c>
       <c r="M27">
-        <v>1.2310925</v>
+        <v>1.2803362</v>
       </c>
       <c r="N27">
-        <v>18.5939075</v>
+        <v>18.5446638</v>
       </c>
       <c r="O27">
-        <v>4.09065965</v>
+        <v>4.079826036</v>
       </c>
       <c r="P27">
-        <v>14.50324785</v>
+        <v>14.464837764</v>
       </c>
       <c r="Q27">
-        <v>15.30324785</v>
+        <v>15.264837764</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1149698084623985</v>
+        <v>0.1157413292775089</v>
       </c>
       <c r="T27">
-        <v>0.9015144823150867</v>
+        <v>0.9115699849063318</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.10358279333194</v>
+        <v>15.48421422435763</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09584942366535662</v>
+        <v>0.09566299098391431</v>
       </c>
       <c r="C28">
-        <v>78.23978935838591</v>
+        <v>77.4646145112423</v>
       </c>
       <c r="D28">
-        <v>94.58378935838591</v>
+        <v>94.78761451124231</v>
       </c>
       <c r="E28">
-        <v>-17.046</v>
+        <v>-16.067</v>
       </c>
       <c r="F28">
-        <v>25.454</v>
+        <v>26.433</v>
       </c>
       <c r="G28">
         <v>9.109999999999999</v>
@@ -3711,28 +3711,28 @@
         <v>19.825</v>
       </c>
       <c r="M28">
-        <v>1.2803362</v>
+        <v>1.3295799</v>
       </c>
       <c r="N28">
-        <v>18.5446638</v>
+        <v>18.4954201</v>
       </c>
       <c r="O28">
-        <v>4.079826036</v>
+        <v>4.068992422</v>
       </c>
       <c r="P28">
-        <v>14.464837764</v>
+        <v>14.426427678</v>
       </c>
       <c r="Q28">
-        <v>15.264837764</v>
+        <v>15.226427678</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1157413292775089</v>
+        <v>0.1165339876491977</v>
       </c>
       <c r="T28">
-        <v>0.9115699849063318</v>
+        <v>0.9219009807192547</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.48421422435763</v>
+        <v>14.91072480864068</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09566299098391431</v>
+        <v>0.09547655830247205</v>
       </c>
       <c r="C29">
-        <v>77.4646145112423</v>
+        <v>76.69032003512415</v>
       </c>
       <c r="D29">
-        <v>94.78761451124231</v>
+        <v>94.99232003512415</v>
       </c>
       <c r="E29">
-        <v>-16.067</v>
+        <v>-15.088</v>
       </c>
       <c r="F29">
-        <v>26.433</v>
+        <v>27.412</v>
       </c>
       <c r="G29">
         <v>9.109999999999999</v>
@@ -3793,28 +3793,28 @@
         <v>19.825</v>
       </c>
       <c r="M29">
-        <v>1.3295799</v>
+        <v>1.3788236</v>
       </c>
       <c r="N29">
-        <v>18.4954201</v>
+        <v>18.4461764</v>
       </c>
       <c r="O29">
-        <v>4.068992422</v>
+        <v>4.058158808</v>
       </c>
       <c r="P29">
-        <v>14.426427678</v>
+        <v>14.388017592</v>
       </c>
       <c r="Q29">
-        <v>15.226427678</v>
+        <v>15.188017592</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1165339876491977</v>
+        <v>0.117348664308989</v>
       </c>
       <c r="T29">
-        <v>0.9219009807192547</v>
+        <v>0.9325189486380924</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.91072480864068</v>
+        <v>14.3781989226178</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09547655830247205</v>
+        <v>0.09529012562102976</v>
       </c>
       <c r="C30">
-        <v>76.69032003512415</v>
+        <v>75.91691164618511</v>
       </c>
       <c r="D30">
-        <v>94.99232003512415</v>
+        <v>95.19791164618512</v>
       </c>
       <c r="E30">
-        <v>-15.088</v>
+        <v>-14.10899999999999</v>
       </c>
       <c r="F30">
-        <v>27.412</v>
+        <v>28.39100000000001</v>
       </c>
       <c r="G30">
         <v>9.109999999999999</v>
@@ -3875,28 +3875,28 @@
         <v>19.825</v>
       </c>
       <c r="M30">
-        <v>1.3788236</v>
+        <v>1.4280673</v>
       </c>
       <c r="N30">
-        <v>18.4461764</v>
+        <v>18.3969327</v>
       </c>
       <c r="O30">
-        <v>4.058158808</v>
+        <v>4.047325194</v>
       </c>
       <c r="P30">
-        <v>14.388017592</v>
+        <v>14.349607506</v>
       </c>
       <c r="Q30">
-        <v>15.188017592</v>
+        <v>15.149607506</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.117348664308989</v>
+        <v>0.1181862896070842</v>
       </c>
       <c r="T30">
-        <v>0.9325189486380924</v>
+        <v>0.9434360142447844</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.3781989226178</v>
+        <v>13.88239895976891</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09529012562102976</v>
+        <v>0.09510369293958745</v>
       </c>
       <c r="C31">
-        <v>75.91691164618513</v>
+        <v>75.14439511017197</v>
       </c>
       <c r="D31">
-        <v>95.19791164618512</v>
+        <v>95.40439511017198</v>
       </c>
       <c r="E31">
-        <v>-14.109</v>
+        <v>-13.13</v>
       </c>
       <c r="F31">
-        <v>28.391</v>
+        <v>29.37</v>
       </c>
       <c r="G31">
         <v>9.109999999999999</v>
@@ -3957,28 +3957,28 @@
         <v>19.825</v>
       </c>
       <c r="M31">
-        <v>1.4280673</v>
+        <v>1.477311</v>
       </c>
       <c r="N31">
-        <v>18.3969327</v>
+        <v>18.347689</v>
       </c>
       <c r="O31">
-        <v>4.047325194</v>
+        <v>4.03649158</v>
       </c>
       <c r="P31">
-        <v>14.349607506</v>
+        <v>14.31119742</v>
       </c>
       <c r="Q31">
-        <v>15.149607506</v>
+        <v>15.11119742</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1181862896070842</v>
+        <v>0.1190478470565535</v>
       </c>
       <c r="T31">
-        <v>0.9434360142447844</v>
+        <v>0.9546649960116678</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.88239895976891</v>
+        <v>13.41965232777661</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09510369293958745</v>
+        <v>0.09491726025814519</v>
       </c>
       <c r="C32">
-        <v>75.14439511017197</v>
+        <v>74.37277624296354</v>
       </c>
       <c r="D32">
-        <v>95.40439511017198</v>
+        <v>95.61177624296354</v>
       </c>
       <c r="E32">
-        <v>-13.13</v>
+        <v>-12.151</v>
       </c>
       <c r="F32">
-        <v>29.37</v>
+        <v>30.349</v>
       </c>
       <c r="G32">
         <v>9.109999999999999</v>
@@ -4039,28 +4039,28 @@
         <v>19.825</v>
       </c>
       <c r="M32">
-        <v>1.477311</v>
+        <v>1.5265547</v>
       </c>
       <c r="N32">
-        <v>18.347689</v>
+        <v>18.2984453</v>
       </c>
       <c r="O32">
-        <v>4.03649158</v>
+        <v>4.025657966</v>
       </c>
       <c r="P32">
-        <v>14.31119742</v>
+        <v>14.272787334</v>
       </c>
       <c r="Q32">
-        <v>15.11119742</v>
+        <v>15.072787334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1190478470565535</v>
+        <v>0.1199343771857177</v>
       </c>
       <c r="T32">
-        <v>0.9546649960116678</v>
+        <v>0.9662194555109246</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.41965232777661</v>
+        <v>12.98676031720318</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09491726025814519</v>
+        <v>0.09510522757670289</v>
       </c>
       <c r="C33">
-        <v>74.37277624296354</v>
+        <v>73.18469176707104</v>
       </c>
       <c r="D33">
-        <v>95.61177624296354</v>
+        <v>95.40269176707105</v>
       </c>
       <c r="E33">
-        <v>-12.151</v>
+        <v>-11.172</v>
       </c>
       <c r="F33">
-        <v>30.349</v>
+        <v>31.328</v>
       </c>
       <c r="G33">
         <v>9.109999999999999</v>
@@ -4121,45 +4121,45 @@
         <v>19.825</v>
       </c>
       <c r="M33">
-        <v>1.5265547</v>
+        <v>1.6227904</v>
       </c>
       <c r="N33">
-        <v>18.2984453</v>
+        <v>18.2022096</v>
       </c>
       <c r="O33">
-        <v>4.025657966</v>
+        <v>4.004486112</v>
       </c>
       <c r="P33">
-        <v>14.272787334</v>
+        <v>14.197723488</v>
       </c>
       <c r="Q33">
-        <v>15.072787334</v>
+        <v>14.997723488</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1199343771857177</v>
+        <v>0.1208469817304454</v>
       </c>
       <c r="T33">
-        <v>0.9662194555109246</v>
+        <v>0.9781137520542771</v>
       </c>
       <c r="U33">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>12.98676031720318</v>
+        <v>12.21661158458911</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09510522757670289</v>
+        <v>0.09493049489526061</v>
       </c>
       <c r="C34">
-        <v>73.18469176707104</v>
+        <v>72.4000247754247</v>
       </c>
       <c r="D34">
-        <v>95.40269176707105</v>
+        <v>95.5970247754247</v>
       </c>
       <c r="E34">
-        <v>-11.172</v>
+        <v>-10.193</v>
       </c>
       <c r="F34">
-        <v>31.328</v>
+        <v>32.307</v>
       </c>
       <c r="G34">
         <v>9.109999999999999</v>
@@ -4203,28 +4203,28 @@
         <v>19.825</v>
       </c>
       <c r="M34">
-        <v>1.6227904</v>
+        <v>1.6735026</v>
       </c>
       <c r="N34">
-        <v>18.2022096</v>
+        <v>18.1514974</v>
       </c>
       <c r="O34">
-        <v>4.004486112</v>
+        <v>3.993329428</v>
       </c>
       <c r="P34">
-        <v>14.197723488</v>
+        <v>14.158167972</v>
       </c>
       <c r="Q34">
-        <v>14.997723488</v>
+        <v>14.958167972</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1208469817304454</v>
+        <v>0.1217868282018815</v>
       </c>
       <c r="T34">
-        <v>0.9781137520542771</v>
+        <v>0.9903631022257894</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.21661158458911</v>
+        <v>11.84641123354096</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09493049489526061</v>
+        <v>0.09475576221381835</v>
       </c>
       <c r="C35">
-        <v>72.4000247754247</v>
+        <v>71.61615110315968</v>
       </c>
       <c r="D35">
-        <v>95.5970247754247</v>
+        <v>95.79215110315968</v>
       </c>
       <c r="E35">
-        <v>-10.193</v>
+        <v>-9.213999999999999</v>
       </c>
       <c r="F35">
-        <v>32.307</v>
+        <v>33.286</v>
       </c>
       <c r="G35">
         <v>9.109999999999999</v>
@@ -4285,28 +4285,28 @@
         <v>19.825</v>
       </c>
       <c r="M35">
-        <v>1.6735026</v>
+        <v>1.7242148</v>
       </c>
       <c r="N35">
-        <v>18.1514974</v>
+        <v>18.1007852</v>
       </c>
       <c r="O35">
-        <v>3.993329428</v>
+        <v>3.982172744</v>
       </c>
       <c r="P35">
-        <v>14.158167972</v>
+        <v>14.118612456</v>
       </c>
       <c r="Q35">
-        <v>14.958167972</v>
+        <v>14.918612456</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1217868282018815</v>
+        <v>0.1227551548694217</v>
       </c>
       <c r="T35">
-        <v>0.9903631022257894</v>
+        <v>1.002983644826742</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.84641123354096</v>
+        <v>11.49798737373093</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09475576221381835</v>
+        <v>0.09458102953237604</v>
       </c>
       <c r="C36">
-        <v>71.61615110315968</v>
+        <v>70.83307561802502</v>
       </c>
       <c r="D36">
-        <v>95.79215110315968</v>
+        <v>95.98807561802504</v>
       </c>
       <c r="E36">
-        <v>-9.213999999999999</v>
+        <v>-8.234999999999992</v>
       </c>
       <c r="F36">
-        <v>33.286</v>
+        <v>34.26500000000001</v>
       </c>
       <c r="G36">
         <v>9.109999999999999</v>
@@ -4367,28 +4367,28 @@
         <v>19.825</v>
       </c>
       <c r="M36">
-        <v>1.7242148</v>
+        <v>1.774927</v>
       </c>
       <c r="N36">
-        <v>18.1007852</v>
+        <v>18.050073</v>
       </c>
       <c r="O36">
-        <v>3.982172744</v>
+        <v>3.971016059999999</v>
       </c>
       <c r="P36">
-        <v>14.118612456</v>
+        <v>14.07905694</v>
       </c>
       <c r="Q36">
-        <v>14.918612456</v>
+        <v>14.87905694</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1227551548694217</v>
+        <v>0.1237532762036555</v>
       </c>
       <c r="T36">
-        <v>1.002983644826742</v>
+        <v>1.015992511815415</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.49798737373093</v>
+        <v>11.16947344876719</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09458102953237604</v>
+        <v>0.09440629685093378</v>
       </c>
       <c r="C37">
-        <v>70.83307561802502</v>
+        <v>70.05080322767549</v>
       </c>
       <c r="D37">
-        <v>95.98807561802504</v>
+        <v>96.18480322767549</v>
       </c>
       <c r="E37">
-        <v>-8.234999999999992</v>
+        <v>-7.255999999999993</v>
       </c>
       <c r="F37">
-        <v>34.26500000000001</v>
+        <v>35.24400000000001</v>
       </c>
       <c r="G37">
         <v>9.109999999999999</v>
@@ -4449,28 +4449,28 @@
         <v>19.825</v>
       </c>
       <c r="M37">
-        <v>1.774927</v>
+        <v>1.8256392</v>
       </c>
       <c r="N37">
-        <v>18.050073</v>
+        <v>17.9993608</v>
       </c>
       <c r="O37">
-        <v>3.971016059999999</v>
+        <v>3.959859375999999</v>
       </c>
       <c r="P37">
-        <v>14.07905694</v>
+        <v>14.039501424</v>
       </c>
       <c r="Q37">
-        <v>14.87905694</v>
+        <v>14.839501424</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1237532762036555</v>
+        <v>0.124782588829584</v>
       </c>
       <c r="T37">
-        <v>1.015992511815415</v>
+        <v>1.029407905897485</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.16947344876719</v>
+        <v>10.85921029741254</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09440629685093377</v>
+        <v>0.09423156416949149</v>
       </c>
       <c r="C38">
-        <v>70.0508032276755</v>
+        <v>69.26933888008143</v>
       </c>
       <c r="D38">
-        <v>96.1848032276755</v>
+        <v>96.38233888008143</v>
       </c>
       <c r="E38">
-        <v>-7.256</v>
+        <v>-6.277000000000001</v>
       </c>
       <c r="F38">
-        <v>35.244</v>
+        <v>36.223</v>
       </c>
       <c r="G38">
         <v>9.109999999999999</v>
@@ -4531,28 +4531,28 @@
         <v>19.825</v>
       </c>
       <c r="M38">
-        <v>1.8256392</v>
+        <v>1.8763514</v>
       </c>
       <c r="N38">
-        <v>17.9993608</v>
+        <v>17.9486486</v>
       </c>
       <c r="O38">
-        <v>3.959859375999999</v>
+        <v>3.948702692</v>
       </c>
       <c r="P38">
-        <v>14.039501424</v>
+        <v>13.999945908</v>
       </c>
       <c r="Q38">
-        <v>14.839501424</v>
+        <v>14.799945908</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.124782588829584</v>
+        <v>0.1258445780468119</v>
       </c>
       <c r="T38">
-        <v>1.029407905897485</v>
+        <v>1.04324918550597</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.85921029741254</v>
+        <v>10.56571812721221</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09423156416949149</v>
+        <v>0.09405683148804921</v>
       </c>
       <c r="C39">
-        <v>69.26933888008143</v>
+        <v>68.48868756394373</v>
       </c>
       <c r="D39">
-        <v>96.38233888008143</v>
+        <v>96.58068756394373</v>
       </c>
       <c r="E39">
-        <v>-6.277000000000001</v>
+        <v>-5.297999999999995</v>
       </c>
       <c r="F39">
-        <v>36.223</v>
+        <v>37.20200000000001</v>
       </c>
       <c r="G39">
         <v>9.109999999999999</v>
@@ -4613,28 +4613,28 @@
         <v>19.825</v>
       </c>
       <c r="M39">
-        <v>1.8763514</v>
+        <v>1.9270636</v>
       </c>
       <c r="N39">
-        <v>17.9486486</v>
+        <v>17.8979364</v>
       </c>
       <c r="O39">
-        <v>3.948702692</v>
+        <v>3.937546008</v>
       </c>
       <c r="P39">
-        <v>13.999945908</v>
+        <v>13.960390392</v>
       </c>
       <c r="Q39">
-        <v>14.799945908</v>
+        <v>14.760390392</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1258445780468119</v>
+        <v>0.1269408249807245</v>
       </c>
       <c r="T39">
-        <v>1.04324918550597</v>
+        <v>1.05753695800505</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.56571812721221</v>
+        <v>10.2876729133382</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09405683148804921</v>
+        <v>0.09388209880660693</v>
       </c>
       <c r="C40">
-        <v>68.48868756394373</v>
+        <v>67.70885430911346</v>
       </c>
       <c r="D40">
-        <v>96.58068756394373</v>
+        <v>96.77985430911346</v>
       </c>
       <c r="E40">
-        <v>-5.297999999999995</v>
+        <v>-4.318999999999996</v>
       </c>
       <c r="F40">
-        <v>37.20200000000001</v>
+        <v>38.181</v>
       </c>
       <c r="G40">
         <v>9.109999999999999</v>
@@ -4695,28 +4695,28 @@
         <v>19.825</v>
       </c>
       <c r="M40">
-        <v>1.9270636</v>
+        <v>1.9777758</v>
       </c>
       <c r="N40">
-        <v>17.8979364</v>
+        <v>17.8472242</v>
       </c>
       <c r="O40">
-        <v>3.937546008</v>
+        <v>3.926389324</v>
       </c>
       <c r="P40">
-        <v>13.960390392</v>
+        <v>13.920834876</v>
       </c>
       <c r="Q40">
-        <v>14.760390392</v>
+        <v>14.720834876</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1269408249807245</v>
+        <v>0.1280730144370605</v>
       </c>
       <c r="T40">
-        <v>1.05753695800505</v>
+        <v>1.072293182061478</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.2876729133382</v>
+        <v>10.02388642838081</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09388209880660693</v>
+        <v>0.09423776612516464</v>
       </c>
       <c r="C41">
-        <v>67.70885430911346</v>
+        <v>66.3253136694313</v>
       </c>
       <c r="D41">
-        <v>96.77985430911346</v>
+        <v>96.37531366943129</v>
       </c>
       <c r="E41">
-        <v>-4.318999999999996</v>
+        <v>-3.339999999999996</v>
       </c>
       <c r="F41">
-        <v>38.181</v>
+        <v>39.16</v>
       </c>
       <c r="G41">
         <v>9.109999999999999</v>
@@ -4777,45 +4777,45 @@
         <v>19.825</v>
       </c>
       <c r="M41">
-        <v>1.9777758</v>
+        <v>2.09506</v>
       </c>
       <c r="N41">
-        <v>17.8472242</v>
+        <v>17.72994</v>
       </c>
       <c r="O41">
-        <v>3.926389324</v>
+        <v>3.9005868</v>
       </c>
       <c r="P41">
-        <v>13.920834876</v>
+        <v>13.8293532</v>
       </c>
       <c r="Q41">
-        <v>14.720834876</v>
+        <v>14.6293532</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1280730144370605</v>
+        <v>0.1292429435419411</v>
       </c>
       <c r="T41">
-        <v>1.072293182061478</v>
+        <v>1.08754128025312</v>
       </c>
       <c r="U41">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>10.02388642838081</v>
+        <v>9.462736150754631</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09423776612516464</v>
+        <v>0.09407629344372237</v>
       </c>
       <c r="C42">
-        <v>66.3253136694313</v>
+        <v>65.52955483543897</v>
       </c>
       <c r="D42">
-        <v>96.37531366943129</v>
+        <v>96.55855483543898</v>
       </c>
       <c r="E42">
-        <v>-3.339999999999996</v>
+        <v>-2.360999999999997</v>
       </c>
       <c r="F42">
-        <v>39.16</v>
+        <v>40.139</v>
       </c>
       <c r="G42">
         <v>9.109999999999999</v>
@@ -4859,28 +4859,28 @@
         <v>19.825</v>
       </c>
       <c r="M42">
-        <v>2.09506</v>
+        <v>2.1474365</v>
       </c>
       <c r="N42">
-        <v>17.72994</v>
+        <v>17.6775635</v>
       </c>
       <c r="O42">
-        <v>3.9005868</v>
+        <v>3.88906397</v>
       </c>
       <c r="P42">
-        <v>13.8293532</v>
+        <v>13.78849953</v>
       </c>
       <c r="Q42">
-        <v>14.6293532</v>
+        <v>14.58849953</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1292429435419411</v>
+        <v>0.1304525312605464</v>
       </c>
       <c r="T42">
-        <v>1.08754128025312</v>
+        <v>1.103306263129225</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.462736150754631</v>
+        <v>9.2319377080533</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09407629344372237</v>
+        <v>0.09391482076228007</v>
       </c>
       <c r="C43">
-        <v>65.52955483543897</v>
+        <v>64.73449413226029</v>
       </c>
       <c r="D43">
-        <v>96.55855483543898</v>
+        <v>96.7424941322603</v>
       </c>
       <c r="E43">
-        <v>-2.360999999999997</v>
+        <v>-1.381999999999991</v>
       </c>
       <c r="F43">
-        <v>40.139</v>
+        <v>41.11800000000001</v>
       </c>
       <c r="G43">
         <v>9.109999999999999</v>
@@ -4941,28 +4941,28 @@
         <v>19.825</v>
       </c>
       <c r="M43">
-        <v>2.1474365</v>
+        <v>2.199813</v>
       </c>
       <c r="N43">
-        <v>17.6775635</v>
+        <v>17.625187</v>
       </c>
       <c r="O43">
-        <v>3.88906397</v>
+        <v>3.87754114</v>
       </c>
       <c r="P43">
-        <v>13.78849953</v>
+        <v>13.74764586</v>
       </c>
       <c r="Q43">
-        <v>14.58849953</v>
+        <v>14.54764586</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1304525312605464</v>
+        <v>0.1317038289004829</v>
       </c>
       <c r="T43">
-        <v>1.103306263129225</v>
+        <v>1.119614866104506</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.2319377080533</v>
+        <v>9.012129667385363</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09391482076228008</v>
+        <v>0.09375334808083781</v>
       </c>
       <c r="C44">
-        <v>64.73449413226029</v>
+        <v>63.94013555722447</v>
       </c>
       <c r="D44">
-        <v>96.74249413226029</v>
+        <v>96.92713555722447</v>
       </c>
       <c r="E44">
-        <v>-1.381999999999998</v>
+        <v>-0.4029999999999987</v>
       </c>
       <c r="F44">
-        <v>41.118</v>
+        <v>42.097</v>
       </c>
       <c r="G44">
         <v>9.109999999999999</v>
@@ -5023,28 +5023,28 @@
         <v>19.825</v>
       </c>
       <c r="M44">
-        <v>2.199813</v>
+        <v>2.2521895</v>
       </c>
       <c r="N44">
-        <v>17.625187</v>
+        <v>17.5728105</v>
       </c>
       <c r="O44">
-        <v>3.87754114</v>
+        <v>3.86601831</v>
       </c>
       <c r="P44">
-        <v>13.74764586</v>
+        <v>13.70679219</v>
       </c>
       <c r="Q44">
-        <v>14.54764586</v>
+        <v>14.50679219</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1317038289004829</v>
+        <v>0.1329990317207681</v>
       </c>
       <c r="T44">
-        <v>1.119614866104506</v>
+        <v>1.136495700763129</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.012129667385363</v>
+        <v>8.802545256515938</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09375334808083781</v>
+        <v>0.09359187539939551</v>
       </c>
       <c r="C45">
-        <v>63.94013555722447</v>
+        <v>63.14648313823623</v>
       </c>
       <c r="D45">
-        <v>96.92713555722447</v>
+        <v>97.11248313823623</v>
       </c>
       <c r="E45">
-        <v>-0.4029999999999987</v>
+        <v>0.5760000000000005</v>
       </c>
       <c r="F45">
-        <v>42.097</v>
+        <v>43.076</v>
       </c>
       <c r="G45">
         <v>9.109999999999999</v>
@@ -5105,28 +5105,28 @@
         <v>19.825</v>
       </c>
       <c r="M45">
-        <v>2.2521895</v>
+        <v>2.304566</v>
       </c>
       <c r="N45">
-        <v>17.5728105</v>
+        <v>17.520434</v>
       </c>
       <c r="O45">
-        <v>3.86601831</v>
+        <v>3.85449548</v>
       </c>
       <c r="P45">
-        <v>13.70679219</v>
+        <v>13.66593852</v>
       </c>
       <c r="Q45">
-        <v>14.50679219</v>
+        <v>14.46593852</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1329990317207681</v>
+        <v>0.1343404917846348</v>
       </c>
       <c r="T45">
-        <v>1.136495700763129</v>
+        <v>1.153979422373847</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.802545256515938</v>
+        <v>8.602487409776938</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09359187539939551</v>
+        <v>0.09343040271795323</v>
       </c>
       <c r="C46">
-        <v>63.14648313823623</v>
+        <v>62.35354093406835</v>
       </c>
       <c r="D46">
-        <v>97.11248313823623</v>
+        <v>97.29854093406836</v>
       </c>
       <c r="E46">
-        <v>0.5760000000000005</v>
+        <v>1.555000000000007</v>
       </c>
       <c r="F46">
-        <v>43.076</v>
+        <v>44.05500000000001</v>
       </c>
       <c r="G46">
         <v>9.109999999999999</v>
@@ -5187,28 +5187,28 @@
         <v>19.825</v>
       </c>
       <c r="M46">
-        <v>2.304566</v>
+        <v>2.3569425</v>
       </c>
       <c r="N46">
-        <v>17.520434</v>
+        <v>17.4680575</v>
       </c>
       <c r="O46">
-        <v>3.85449548</v>
+        <v>3.84297265</v>
       </c>
       <c r="P46">
-        <v>13.66593852</v>
+        <v>13.62508485</v>
       </c>
       <c r="Q46">
-        <v>14.46593852</v>
+        <v>14.42508485</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1343404917846348</v>
+        <v>0.1357307322144604</v>
       </c>
       <c r="T46">
-        <v>1.153979422373847</v>
+        <v>1.172098915679499</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.602487409776938</v>
+        <v>8.411321022893006</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09343040271795323</v>
+        <v>0.09326893003651095</v>
       </c>
       <c r="C47">
-        <v>62.35354093406835</v>
+        <v>61.5613130346583</v>
       </c>
       <c r="D47">
-        <v>97.29854093406836</v>
+        <v>97.4853130346583</v>
       </c>
       <c r="E47">
-        <v>1.555000000000007</v>
+        <v>2.534000000000006</v>
       </c>
       <c r="F47">
-        <v>44.05500000000001</v>
+        <v>45.03400000000001</v>
       </c>
       <c r="G47">
         <v>9.109999999999999</v>
@@ -5269,28 +5269,28 @@
         <v>19.825</v>
       </c>
       <c r="M47">
-        <v>2.3569425</v>
+        <v>2.409319</v>
       </c>
       <c r="N47">
-        <v>17.4680575</v>
+        <v>17.415681</v>
       </c>
       <c r="O47">
-        <v>3.84297265</v>
+        <v>3.83144982</v>
       </c>
       <c r="P47">
-        <v>13.62508485</v>
+        <v>13.58423118</v>
       </c>
       <c r="Q47">
-        <v>14.42508485</v>
+        <v>14.38423118</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1357307322144604</v>
+        <v>0.1371724630305758</v>
       </c>
       <c r="T47">
-        <v>1.172098915679499</v>
+        <v>1.190889501329806</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.411321022893006</v>
+        <v>8.228466218047505</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09326893003651095</v>
+        <v>0.09310745735506867</v>
       </c>
       <c r="C48">
-        <v>61.5613130346583</v>
+        <v>60.76980356140767</v>
       </c>
       <c r="D48">
-        <v>97.4853130346583</v>
+        <v>97.67280356140768</v>
       </c>
       <c r="E48">
-        <v>2.534000000000006</v>
+        <v>3.513000000000005</v>
       </c>
       <c r="F48">
-        <v>45.03400000000001</v>
+        <v>46.01300000000001</v>
       </c>
       <c r="G48">
         <v>9.109999999999999</v>
@@ -5351,28 +5351,28 @@
         <v>19.825</v>
       </c>
       <c r="M48">
-        <v>2.409319</v>
+        <v>2.4616955</v>
       </c>
       <c r="N48">
-        <v>17.415681</v>
+        <v>17.3633045</v>
       </c>
       <c r="O48">
-        <v>3.83144982</v>
+        <v>3.819926989999999</v>
       </c>
       <c r="P48">
-        <v>13.58423118</v>
+        <v>13.54337751</v>
       </c>
       <c r="Q48">
-        <v>14.38423118</v>
+        <v>14.34337751</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1371724630305758</v>
+        <v>0.1386685987831484</v>
       </c>
       <c r="T48">
-        <v>1.190889501329806</v>
+        <v>1.210389165683897</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.228466218047505</v>
+        <v>8.053392468727345</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09310745735506867</v>
+        <v>0.09294598467362639</v>
       </c>
       <c r="C49">
-        <v>60.76980356140767</v>
+        <v>59.97901666748542</v>
       </c>
       <c r="D49">
-        <v>97.67280356140768</v>
+        <v>97.86101666748543</v>
       </c>
       <c r="E49">
-        <v>3.513000000000005</v>
+        <v>4.492000000000004</v>
       </c>
       <c r="F49">
-        <v>46.01300000000001</v>
+        <v>46.992</v>
       </c>
       <c r="G49">
         <v>9.109999999999999</v>
@@ -5433,28 +5433,28 @@
         <v>19.825</v>
       </c>
       <c r="M49">
-        <v>2.4616955</v>
+        <v>2.514072</v>
       </c>
       <c r="N49">
-        <v>17.3633045</v>
+        <v>17.310928</v>
       </c>
       <c r="O49">
-        <v>3.819926989999999</v>
+        <v>3.80840416</v>
       </c>
       <c r="P49">
-        <v>13.54337751</v>
+        <v>13.50252384</v>
       </c>
       <c r="Q49">
-        <v>14.34337751</v>
+        <v>14.30252384</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1386685987831484</v>
+        <v>0.1402222782185123</v>
       </c>
       <c r="T49">
-        <v>1.210389165683897</v>
+        <v>1.230638817128531</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.053392468727345</v>
+        <v>7.885613458962194</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09294598467362639</v>
+        <v>0.0927845119921841</v>
       </c>
       <c r="C50">
-        <v>59.97901666748542</v>
+        <v>59.18895653813458</v>
       </c>
       <c r="D50">
-        <v>97.86101666748543</v>
+        <v>98.04995653813458</v>
       </c>
       <c r="E50">
-        <v>4.492000000000004</v>
+        <v>5.471000000000004</v>
       </c>
       <c r="F50">
-        <v>46.992</v>
+        <v>47.971</v>
       </c>
       <c r="G50">
         <v>9.109999999999999</v>
@@ -5515,28 +5515,28 @@
         <v>19.825</v>
       </c>
       <c r="M50">
-        <v>2.514072</v>
+        <v>2.5664485</v>
       </c>
       <c r="N50">
-        <v>17.310928</v>
+        <v>17.2585515</v>
       </c>
       <c r="O50">
-        <v>3.80840416</v>
+        <v>3.79688133</v>
       </c>
       <c r="P50">
-        <v>13.50252384</v>
+        <v>13.46167017</v>
       </c>
       <c r="Q50">
-        <v>14.30252384</v>
+        <v>14.26167017</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1402222782185123</v>
+        <v>0.1418368862591845</v>
       </c>
       <c r="T50">
-        <v>1.230638817128531</v>
+        <v>1.251682572551386</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.885613458962194</v>
+        <v>7.724682572044597</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0927845119921841</v>
+        <v>0.09293503931074182</v>
       </c>
       <c r="C51">
-        <v>59.18895653813458</v>
+        <v>58.0338008737756</v>
       </c>
       <c r="D51">
-        <v>98.04995653813458</v>
+        <v>97.87380087377561</v>
       </c>
       <c r="E51">
-        <v>5.471000000000004</v>
+        <v>6.450000000000003</v>
       </c>
       <c r="F51">
-        <v>47.971</v>
+        <v>48.95</v>
       </c>
       <c r="G51">
         <v>9.109999999999999</v>
@@ -5597,45 +5597,45 @@
         <v>19.825</v>
       </c>
       <c r="M51">
-        <v>2.5664485</v>
+        <v>2.657985</v>
       </c>
       <c r="N51">
-        <v>17.2585515</v>
+        <v>17.167015</v>
       </c>
       <c r="O51">
-        <v>3.79688133</v>
+        <v>3.7767433</v>
       </c>
       <c r="P51">
-        <v>13.46167017</v>
+        <v>13.3902717</v>
       </c>
       <c r="Q51">
-        <v>14.26167017</v>
+        <v>14.1902717</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1418368862591845</v>
+        <v>0.1435160786214836</v>
       </c>
       <c r="T51">
-        <v>1.251682572551386</v>
+        <v>1.273568078191154</v>
       </c>
       <c r="U51">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V51">
         <v>0.22</v>
       </c>
       <c r="W51">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.724682572044597</v>
+        <v>7.458657592123356</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09293503931074182</v>
+        <v>0.09277980662929954</v>
       </c>
       <c r="C52">
-        <v>58.0338008737756</v>
+        <v>57.23647324357302</v>
       </c>
       <c r="D52">
-        <v>97.87380087377561</v>
+        <v>98.05547324357302</v>
       </c>
       <c r="E52">
-        <v>6.450000000000003</v>
+        <v>7.429000000000002</v>
       </c>
       <c r="F52">
-        <v>48.95</v>
+        <v>49.929</v>
       </c>
       <c r="G52">
         <v>9.109999999999999</v>
@@ -5679,28 +5679,28 @@
         <v>19.825</v>
       </c>
       <c r="M52">
-        <v>2.657985</v>
+        <v>2.7111447</v>
       </c>
       <c r="N52">
-        <v>17.167015</v>
+        <v>17.1138553</v>
       </c>
       <c r="O52">
-        <v>3.7767433</v>
+        <v>3.765048165999999</v>
       </c>
       <c r="P52">
-        <v>13.3902717</v>
+        <v>13.348807134</v>
       </c>
       <c r="Q52">
-        <v>14.1902717</v>
+        <v>14.148807134</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1435160786214836</v>
+        <v>0.1452638094475501</v>
       </c>
       <c r="T52">
-        <v>1.273568078191154</v>
+        <v>1.296346869775403</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.458657592123356</v>
+        <v>7.312409404042505</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09277980662929954</v>
+        <v>0.09262457394785725</v>
       </c>
       <c r="C53">
-        <v>57.23647324357302</v>
+        <v>56.43982130445124</v>
       </c>
       <c r="D53">
-        <v>98.05547324357302</v>
+        <v>98.23782130445124</v>
       </c>
       <c r="E53">
-        <v>7.429000000000002</v>
+        <v>8.408000000000001</v>
       </c>
       <c r="F53">
-        <v>49.929</v>
+        <v>50.908</v>
       </c>
       <c r="G53">
         <v>9.109999999999999</v>
@@ -5761,28 +5761,28 @@
         <v>19.825</v>
       </c>
       <c r="M53">
-        <v>2.7111447</v>
+        <v>2.7643044</v>
       </c>
       <c r="N53">
-        <v>17.1138553</v>
+        <v>17.0606956</v>
       </c>
       <c r="O53">
-        <v>3.765048165999999</v>
+        <v>3.753353032</v>
       </c>
       <c r="P53">
-        <v>13.348807134</v>
+        <v>13.307342568</v>
       </c>
       <c r="Q53">
-        <v>14.148807134</v>
+        <v>14.107342568</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1452638094475501</v>
+        <v>0.1470843623913693</v>
       </c>
       <c r="T53">
-        <v>1.296346869775403</v>
+        <v>1.320074777675663</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.312409404042505</v>
+        <v>7.171786146272457</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09262457394785725</v>
+        <v>0.09246934126641497</v>
       </c>
       <c r="C54">
-        <v>56.43982130445124</v>
+        <v>55.64384883306372</v>
       </c>
       <c r="D54">
-        <v>98.23782130445124</v>
+        <v>98.42084883306373</v>
       </c>
       <c r="E54">
-        <v>8.408000000000001</v>
+        <v>9.387000000000008</v>
       </c>
       <c r="F54">
-        <v>50.908</v>
+        <v>51.88700000000001</v>
       </c>
       <c r="G54">
         <v>9.109999999999999</v>
@@ -5843,28 +5843,28 @@
         <v>19.825</v>
       </c>
       <c r="M54">
-        <v>2.7643044</v>
+        <v>2.8174641</v>
       </c>
       <c r="N54">
-        <v>17.0606956</v>
+        <v>17.0075359</v>
       </c>
       <c r="O54">
-        <v>3.753353032</v>
+        <v>3.741657898</v>
       </c>
       <c r="P54">
-        <v>13.307342568</v>
+        <v>13.265878002</v>
       </c>
       <c r="Q54">
-        <v>14.107342568</v>
+        <v>14.065878002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1470843623913693</v>
+        <v>0.1489823856732233</v>
       </c>
       <c r="T54">
-        <v>1.320074777675663</v>
+        <v>1.344812383784444</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.171786146272457</v>
+        <v>7.036469426531467</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09246934126641497</v>
+        <v>0.09231410858497267</v>
       </c>
       <c r="C55">
-        <v>55.64384883306372</v>
+        <v>54.84855963426168</v>
       </c>
       <c r="D55">
-        <v>98.42084883306373</v>
+        <v>98.60455963426169</v>
       </c>
       <c r="E55">
-        <v>9.387000000000008</v>
+        <v>10.36600000000001</v>
       </c>
       <c r="F55">
-        <v>51.88700000000001</v>
+        <v>52.86600000000001</v>
       </c>
       <c r="G55">
         <v>9.109999999999999</v>
@@ -5925,28 +5925,28 @@
         <v>19.825</v>
       </c>
       <c r="M55">
-        <v>2.8174641</v>
+        <v>2.870623800000001</v>
       </c>
       <c r="N55">
-        <v>17.0075359</v>
+        <v>16.9543762</v>
       </c>
       <c r="O55">
-        <v>3.741657898</v>
+        <v>3.729962764</v>
       </c>
       <c r="P55">
-        <v>13.265878002</v>
+        <v>13.224413436</v>
       </c>
       <c r="Q55">
-        <v>14.065878002</v>
+        <v>14.024413436</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1489823856732233</v>
+        <v>0.1509629317064624</v>
       </c>
       <c r="T55">
-        <v>1.344812383784444</v>
+        <v>1.370625537984911</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.036469426531467</v>
+        <v>6.906164437151254</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09231410858497267</v>
+        <v>0.09215887590353039</v>
       </c>
       <c r="C56">
-        <v>54.84855963426168</v>
+        <v>54.05395754135771</v>
       </c>
       <c r="D56">
-        <v>98.60455963426169</v>
+        <v>98.78895754135772</v>
       </c>
       <c r="E56">
-        <v>10.36600000000001</v>
+        <v>11.34500000000001</v>
       </c>
       <c r="F56">
-        <v>52.86600000000001</v>
+        <v>53.84500000000001</v>
       </c>
       <c r="G56">
         <v>9.109999999999999</v>
@@ -6007,28 +6007,28 @@
         <v>19.825</v>
       </c>
       <c r="M56">
-        <v>2.870623800000001</v>
+        <v>2.9237835</v>
       </c>
       <c r="N56">
-        <v>16.9543762</v>
+        <v>16.9012165</v>
       </c>
       <c r="O56">
-        <v>3.729962764</v>
+        <v>3.71826763</v>
       </c>
       <c r="P56">
-        <v>13.224413436</v>
+        <v>13.18294887</v>
       </c>
       <c r="Q56">
-        <v>14.024413436</v>
+        <v>13.98294887</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1509629317064624</v>
+        <v>0.1530315020078453</v>
       </c>
       <c r="T56">
-        <v>1.370625537984911</v>
+        <v>1.397585943483177</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.906164437151254</v>
+        <v>6.780597811021233</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09215887590353039</v>
+        <v>0.09200364322208811</v>
       </c>
       <c r="C57">
-        <v>54.05395754135771</v>
+        <v>53.26004641639253</v>
       </c>
       <c r="D57">
-        <v>98.78895754135772</v>
+        <v>98.97404641639254</v>
       </c>
       <c r="E57">
-        <v>11.34500000000001</v>
+        <v>12.32400000000001</v>
       </c>
       <c r="F57">
-        <v>53.84500000000001</v>
+        <v>54.82400000000001</v>
       </c>
       <c r="G57">
         <v>9.109999999999999</v>
@@ -6089,28 +6089,28 @@
         <v>19.825</v>
       </c>
       <c r="M57">
-        <v>2.9237835</v>
+        <v>2.9769432</v>
       </c>
       <c r="N57">
-        <v>16.9012165</v>
+        <v>16.8480568</v>
       </c>
       <c r="O57">
-        <v>3.71826763</v>
+        <v>3.706572496</v>
       </c>
       <c r="P57">
-        <v>13.18294887</v>
+        <v>13.141484304</v>
       </c>
       <c r="Q57">
-        <v>13.98294887</v>
+        <v>13.941484304</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1530315020078453</v>
+        <v>0.1551940982320184</v>
       </c>
       <c r="T57">
-        <v>1.397585943483177</v>
+        <v>1.425771821958636</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.780597811021233</v>
+        <v>6.659515707252996</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09200364322208811</v>
+        <v>0.09184841054064583</v>
       </c>
       <c r="C58">
-        <v>53.26004641639253</v>
+        <v>52.46683015040448</v>
       </c>
       <c r="D58">
-        <v>98.97404641639254</v>
+        <v>99.15983015040449</v>
       </c>
       <c r="E58">
-        <v>12.32400000000001</v>
+        <v>13.30300000000001</v>
       </c>
       <c r="F58">
-        <v>54.82400000000001</v>
+        <v>55.80300000000001</v>
       </c>
       <c r="G58">
         <v>9.109999999999999</v>
@@ -6171,28 +6171,28 @@
         <v>19.825</v>
       </c>
       <c r="M58">
-        <v>2.9769432</v>
+        <v>3.030102900000001</v>
       </c>
       <c r="N58">
-        <v>16.8480568</v>
+        <v>16.7948971</v>
       </c>
       <c r="O58">
-        <v>3.706572496</v>
+        <v>3.694877362</v>
       </c>
       <c r="P58">
-        <v>13.141484304</v>
+        <v>13.100019738</v>
       </c>
       <c r="Q58">
-        <v>13.941484304</v>
+        <v>13.900019738</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1551940982320184</v>
+        <v>0.1574572803270833</v>
       </c>
       <c r="T58">
-        <v>1.425771821958636</v>
+        <v>1.455268671525978</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.659515707252996</v>
+        <v>6.54268209835382</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09184841054064583</v>
+        <v>0.09169317785920354</v>
       </c>
       <c r="C59">
-        <v>52.46683015040448</v>
+        <v>51.67431266370225</v>
       </c>
       <c r="D59">
-        <v>99.15983015040449</v>
+        <v>99.34631266370226</v>
       </c>
       <c r="E59">
-        <v>13.30300000000001</v>
+        <v>14.28200000000001</v>
       </c>
       <c r="F59">
-        <v>55.80300000000001</v>
+        <v>56.78200000000001</v>
       </c>
       <c r="G59">
         <v>9.109999999999999</v>
@@ -6253,28 +6253,28 @@
         <v>19.825</v>
       </c>
       <c r="M59">
-        <v>3.030102900000001</v>
+        <v>3.083262600000001</v>
       </c>
       <c r="N59">
-        <v>16.7948971</v>
+        <v>16.7417374</v>
       </c>
       <c r="O59">
-        <v>3.694877362</v>
+        <v>3.683182228</v>
       </c>
       <c r="P59">
-        <v>13.100019738</v>
+        <v>13.058555172</v>
       </c>
       <c r="Q59">
-        <v>13.900019738</v>
+        <v>13.858555172</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1574572803270833</v>
+        <v>0.1598282329981037</v>
       </c>
       <c r="T59">
-        <v>1.455268671525978</v>
+        <v>1.486170132977479</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.54268209835382</v>
+        <v>6.429877234589099</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09169317785920356</v>
+        <v>0.09153794517776126</v>
       </c>
       <c r="C60">
-        <v>51.67431266370227</v>
+        <v>50.88249790614072</v>
       </c>
       <c r="D60">
-        <v>99.34631266370226</v>
+        <v>99.53349790614072</v>
       </c>
       <c r="E60">
-        <v>14.282</v>
+        <v>15.261</v>
       </c>
       <c r="F60">
-        <v>56.782</v>
+        <v>57.761</v>
       </c>
       <c r="G60">
         <v>9.109999999999999</v>
@@ -6335,28 +6335,28 @@
         <v>19.825</v>
       </c>
       <c r="M60">
-        <v>3.0832626</v>
+        <v>3.1364223</v>
       </c>
       <c r="N60">
-        <v>16.7417374</v>
+        <v>16.6885777</v>
       </c>
       <c r="O60">
-        <v>3.683182228</v>
+        <v>3.671487094</v>
       </c>
       <c r="P60">
-        <v>13.058555172</v>
+        <v>13.017090606</v>
       </c>
       <c r="Q60">
-        <v>13.858555172</v>
+        <v>13.817090606</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1598282329981037</v>
+        <v>0.1623148418969787</v>
       </c>
       <c r="T60">
-        <v>1.486170132977478</v>
+        <v>1.518578982792467</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.4298772345891</v>
+        <v>6.320896264511319</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09153794517776126</v>
+        <v>0.09138271249631898</v>
       </c>
       <c r="C61">
-        <v>50.88249790614072</v>
+        <v>50.09138985739957</v>
       </c>
       <c r="D61">
-        <v>99.53349790614072</v>
+        <v>99.72138985739957</v>
       </c>
       <c r="E61">
-        <v>15.261</v>
+        <v>16.24</v>
       </c>
       <c r="F61">
-        <v>57.761</v>
+        <v>58.74</v>
       </c>
       <c r="G61">
         <v>9.109999999999999</v>
@@ -6417,28 +6417,28 @@
         <v>19.825</v>
       </c>
       <c r="M61">
-        <v>3.1364223</v>
+        <v>3.189582</v>
       </c>
       <c r="N61">
-        <v>16.6885777</v>
+        <v>16.635418</v>
       </c>
       <c r="O61">
-        <v>3.671487094</v>
+        <v>3.65979196</v>
       </c>
       <c r="P61">
-        <v>13.017090606</v>
+        <v>12.97562604</v>
       </c>
       <c r="Q61">
-        <v>13.817090606</v>
+        <v>13.77562604</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1623148418969787</v>
+        <v>0.1649257812407974</v>
       </c>
       <c r="T61">
-        <v>1.518578982792467</v>
+        <v>1.552608275098205</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.320896264511319</v>
+        <v>6.21554799343613</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09138271249631898</v>
+        <v>0.09122747981487669</v>
       </c>
       <c r="C62">
-        <v>50.09138985739957</v>
+        <v>49.30099252726563</v>
       </c>
       <c r="D62">
-        <v>99.72138985739957</v>
+        <v>99.90999252726563</v>
       </c>
       <c r="E62">
-        <v>16.24</v>
+        <v>17.219</v>
       </c>
       <c r="F62">
-        <v>58.74</v>
+        <v>59.719</v>
       </c>
       <c r="G62">
         <v>9.109999999999999</v>
@@ -6499,28 +6499,28 @@
         <v>19.825</v>
       </c>
       <c r="M62">
-        <v>3.189582</v>
+        <v>3.2427417</v>
       </c>
       <c r="N62">
-        <v>16.635418</v>
+        <v>16.5822583</v>
       </c>
       <c r="O62">
-        <v>3.65979196</v>
+        <v>3.648096826</v>
       </c>
       <c r="P62">
-        <v>12.97562604</v>
+        <v>12.934161474</v>
       </c>
       <c r="Q62">
-        <v>13.77562604</v>
+        <v>13.734161474</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1649257812407974</v>
+        <v>0.1676706149099402</v>
       </c>
       <c r="T62">
-        <v>1.552608275098205</v>
+        <v>1.588382659317057</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.21554799343613</v>
+        <v>6.113653764035537</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09122747981487669</v>
+        <v>0.09155584713343441</v>
       </c>
       <c r="C63">
-        <v>49.30099252726563</v>
+        <v>47.92387509866322</v>
       </c>
       <c r="D63">
-        <v>99.90999252726563</v>
+        <v>99.51187509866323</v>
       </c>
       <c r="E63">
-        <v>17.219</v>
+        <v>18.198</v>
       </c>
       <c r="F63">
-        <v>59.719</v>
+        <v>60.698</v>
       </c>
       <c r="G63">
         <v>9.109999999999999</v>
@@ -6581,45 +6581,45 @@
         <v>19.825</v>
       </c>
       <c r="M63">
-        <v>3.2427417</v>
+        <v>3.3565994</v>
       </c>
       <c r="N63">
-        <v>16.5822583</v>
+        <v>16.4684006</v>
       </c>
       <c r="O63">
-        <v>3.648096826</v>
+        <v>3.623048132</v>
       </c>
       <c r="P63">
-        <v>12.934161474</v>
+        <v>12.845352468</v>
       </c>
       <c r="Q63">
-        <v>13.734161474</v>
+        <v>13.645352468</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1676706149099402</v>
+        <v>0.1705599135090379</v>
       </c>
       <c r="T63">
-        <v>1.588382659317057</v>
+        <v>1.626039905863218</v>
       </c>
       <c r="U63">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V63">
         <v>0.22</v>
       </c>
       <c r="W63">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>6.113653764035537</v>
+        <v>5.906275261802167</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09155584713343441</v>
+        <v>0.09140841445199213</v>
       </c>
       <c r="C64">
-        <v>47.92387509866322</v>
+        <v>47.12323150210601</v>
       </c>
       <c r="D64">
-        <v>99.51187509866323</v>
+        <v>99.69023150210602</v>
       </c>
       <c r="E64">
-        <v>18.198</v>
+        <v>19.17700000000001</v>
       </c>
       <c r="F64">
-        <v>60.698</v>
+        <v>61.67700000000001</v>
       </c>
       <c r="G64">
         <v>9.109999999999999</v>
@@ -6663,28 +6663,28 @@
         <v>19.825</v>
       </c>
       <c r="M64">
-        <v>3.3565994</v>
+        <v>3.410738100000001</v>
       </c>
       <c r="N64">
-        <v>16.4684006</v>
+        <v>16.4142619</v>
       </c>
       <c r="O64">
-        <v>3.623048132</v>
+        <v>3.611137618</v>
       </c>
       <c r="P64">
-        <v>12.845352468</v>
+        <v>12.803124282</v>
       </c>
       <c r="Q64">
-        <v>13.645352468</v>
+        <v>13.603124282</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1705599135090379</v>
+        <v>0.1736053904107895</v>
       </c>
       <c r="T64">
-        <v>1.626039905863218</v>
+        <v>1.665732679249712</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.906275261802167</v>
+        <v>5.81252486082118</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09140841445199213</v>
+        <v>0.09126098177054986</v>
       </c>
       <c r="C65">
-        <v>47.12323150210601</v>
+        <v>46.32322839442031</v>
       </c>
       <c r="D65">
-        <v>99.69023150210602</v>
+        <v>99.86922839442032</v>
       </c>
       <c r="E65">
-        <v>19.17700000000001</v>
+        <v>20.15600000000001</v>
       </c>
       <c r="F65">
-        <v>61.67700000000001</v>
+        <v>62.65600000000001</v>
       </c>
       <c r="G65">
         <v>9.109999999999999</v>
@@ -6745,28 +6745,28 @@
         <v>19.825</v>
       </c>
       <c r="M65">
-        <v>3.410738100000001</v>
+        <v>3.4648768</v>
       </c>
       <c r="N65">
-        <v>16.4142619</v>
+        <v>16.3601232</v>
       </c>
       <c r="O65">
-        <v>3.611137618</v>
+        <v>3.599227104</v>
       </c>
       <c r="P65">
-        <v>12.803124282</v>
+        <v>12.760896096</v>
       </c>
       <c r="Q65">
-        <v>13.603124282</v>
+        <v>13.560896096</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1736053904107895</v>
+        <v>0.1768200604737496</v>
       </c>
       <c r="T65">
-        <v>1.665732679249712</v>
+        <v>1.707630606713233</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.81252486082118</v>
+        <v>5.72170415987085</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09126098177054986</v>
+        <v>0.09111354908910757</v>
       </c>
       <c r="C66">
-        <v>46.32322839442031</v>
+        <v>45.52386923186475</v>
       </c>
       <c r="D66">
-        <v>99.86922839442032</v>
+        <v>100.0488692318648</v>
       </c>
       <c r="E66">
-        <v>20.15600000000001</v>
+        <v>21.13500000000001</v>
       </c>
       <c r="F66">
-        <v>62.65600000000001</v>
+        <v>63.63500000000001</v>
       </c>
       <c r="G66">
         <v>9.109999999999999</v>
@@ -6827,28 +6827,28 @@
         <v>19.825</v>
       </c>
       <c r="M66">
-        <v>3.4648768</v>
+        <v>3.519015500000001</v>
       </c>
       <c r="N66">
-        <v>16.3601232</v>
+        <v>16.3059845</v>
       </c>
       <c r="O66">
-        <v>3.599227104</v>
+        <v>3.587316589999999</v>
       </c>
       <c r="P66">
-        <v>12.760896096</v>
+        <v>12.71866791</v>
       </c>
       <c r="Q66">
-        <v>13.560896096</v>
+        <v>13.51866791</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1768200604737496</v>
+        <v>0.1802184259688788</v>
       </c>
       <c r="T66">
-        <v>1.707630606713233</v>
+        <v>1.751922701460384</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.72170415987085</v>
+        <v>5.633677942026682</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09111354908910757</v>
+        <v>0.0909661164076653</v>
       </c>
       <c r="C67">
-        <v>45.52386923186475</v>
+        <v>44.7251574956105</v>
       </c>
       <c r="D67">
-        <v>100.0488692318648</v>
+        <v>100.2291574956105</v>
       </c>
       <c r="E67">
-        <v>21.13500000000001</v>
+        <v>22.114</v>
       </c>
       <c r="F67">
-        <v>63.63500000000001</v>
+        <v>64.614</v>
       </c>
       <c r="G67">
         <v>9.109999999999999</v>
@@ -6909,28 +6909,28 @@
         <v>19.825</v>
       </c>
       <c r="M67">
-        <v>3.519015500000001</v>
+        <v>3.5731542</v>
       </c>
       <c r="N67">
-        <v>16.3059845</v>
+        <v>16.2518458</v>
       </c>
       <c r="O67">
-        <v>3.587316589999999</v>
+        <v>3.575406076</v>
       </c>
       <c r="P67">
-        <v>12.71866791</v>
+        <v>12.676439724</v>
       </c>
       <c r="Q67">
-        <v>13.51866791</v>
+        <v>13.476439724</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1802184259688788</v>
+        <v>0.1838166953166626</v>
       </c>
       <c r="T67">
-        <v>1.751922701460384</v>
+        <v>1.798820213545603</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.633677942026682</v>
+        <v>5.548319185329309</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0909661164076653</v>
+        <v>0.09081868372622301</v>
       </c>
       <c r="C68">
-        <v>44.7251574956105</v>
+        <v>43.92709669196654</v>
       </c>
       <c r="D68">
-        <v>100.2291574956105</v>
+        <v>100.4100966919665</v>
       </c>
       <c r="E68">
-        <v>22.114</v>
+        <v>23.093</v>
       </c>
       <c r="F68">
-        <v>64.614</v>
+        <v>65.593</v>
       </c>
       <c r="G68">
         <v>9.109999999999999</v>
@@ -6991,28 +6991,28 @@
         <v>19.825</v>
       </c>
       <c r="M68">
-        <v>3.5731542</v>
+        <v>3.6272929</v>
       </c>
       <c r="N68">
-        <v>16.2518458</v>
+        <v>16.1977071</v>
       </c>
       <c r="O68">
-        <v>3.575406076</v>
+        <v>3.563495562</v>
       </c>
       <c r="P68">
-        <v>12.676439724</v>
+        <v>12.634211538</v>
       </c>
       <c r="Q68">
-        <v>13.476439724</v>
+        <v>13.434211538</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1838166953166626</v>
+        <v>0.1876330415946152</v>
       </c>
       <c r="T68">
-        <v>1.798820213545603</v>
+        <v>1.848559999090531</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.548319185329309</v>
+        <v>5.465508451219915</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09081868372622301</v>
+        <v>0.09067125104478073</v>
       </c>
       <c r="C69">
-        <v>43.92709669196654</v>
+        <v>43.12969035260656</v>
       </c>
       <c r="D69">
-        <v>100.4100966919665</v>
+        <v>100.5916903526066</v>
       </c>
       <c r="E69">
-        <v>23.093</v>
+        <v>24.072</v>
       </c>
       <c r="F69">
-        <v>65.593</v>
+        <v>66.572</v>
       </c>
       <c r="G69">
         <v>9.109999999999999</v>
@@ -7073,28 +7073,28 @@
         <v>19.825</v>
       </c>
       <c r="M69">
-        <v>3.6272929</v>
+        <v>3.6814316</v>
       </c>
       <c r="N69">
-        <v>16.1977071</v>
+        <v>16.1435684</v>
       </c>
       <c r="O69">
-        <v>3.563495562</v>
+        <v>3.551585048</v>
       </c>
       <c r="P69">
-        <v>12.634211538</v>
+        <v>12.591983352</v>
       </c>
       <c r="Q69">
-        <v>13.434211538</v>
+        <v>13.391983352</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1876330415946152</v>
+        <v>0.1916879095149398</v>
       </c>
       <c r="T69">
-        <v>1.848559999090531</v>
+        <v>1.901408521232019</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.465508451219915</v>
+        <v>5.385133326937271</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09067125104478073</v>
+        <v>0.09052381836333845</v>
       </c>
       <c r="C70">
-        <v>43.12969035260656</v>
+        <v>42.33294203479905</v>
       </c>
       <c r="D70">
-        <v>100.5916903526066</v>
+        <v>100.7739420347991</v>
       </c>
       <c r="E70">
-        <v>24.072</v>
+        <v>25.05100000000002</v>
       </c>
       <c r="F70">
-        <v>66.572</v>
+        <v>67.55100000000002</v>
       </c>
       <c r="G70">
         <v>9.109999999999999</v>
@@ -7155,28 +7155,28 @@
         <v>19.825</v>
       </c>
       <c r="M70">
-        <v>3.6814316</v>
+        <v>3.735570300000001</v>
       </c>
       <c r="N70">
-        <v>16.1435684</v>
+        <v>16.0894297</v>
       </c>
       <c r="O70">
-        <v>3.551585048</v>
+        <v>3.539674533999999</v>
       </c>
       <c r="P70">
-        <v>12.591983352</v>
+        <v>12.549755166</v>
       </c>
       <c r="Q70">
-        <v>13.391983352</v>
+        <v>13.349755166</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1916879095149398</v>
+        <v>0.1960043818172208</v>
       </c>
       <c r="T70">
-        <v>1.901408521232019</v>
+        <v>1.95766662544715</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.385133326937271</v>
+        <v>5.307087916401946</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09052381836333845</v>
+        <v>0.09037638568189615</v>
       </c>
       <c r="C71">
-        <v>42.33294203479905</v>
+        <v>41.53685532163954</v>
       </c>
       <c r="D71">
-        <v>100.7739420347991</v>
+        <v>100.9568553216396</v>
       </c>
       <c r="E71">
-        <v>25.05100000000002</v>
+        <v>26.03000000000002</v>
       </c>
       <c r="F71">
-        <v>67.55100000000002</v>
+        <v>68.53000000000002</v>
       </c>
       <c r="G71">
         <v>9.109999999999999</v>
@@ -7237,28 +7237,28 @@
         <v>19.825</v>
       </c>
       <c r="M71">
-        <v>3.735570300000001</v>
+        <v>3.789709000000001</v>
       </c>
       <c r="N71">
-        <v>16.0894297</v>
+        <v>16.035291</v>
       </c>
       <c r="O71">
-        <v>3.539674533999999</v>
+        <v>3.527764019999999</v>
       </c>
       <c r="P71">
-        <v>12.549755166</v>
+        <v>12.50752698</v>
       </c>
       <c r="Q71">
-        <v>13.349755166</v>
+        <v>13.30752698</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1960043818172208</v>
+        <v>0.2006086189396539</v>
       </c>
       <c r="T71">
-        <v>1.95766662544715</v>
+        <v>2.01767526994329</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.307087916401946</v>
+        <v>5.231272374739061</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09037638568189615</v>
+        <v>0.09022895300045389</v>
       </c>
       <c r="C72">
-        <v>41.53685532163954</v>
+        <v>40.74143382228525</v>
       </c>
       <c r="D72">
-        <v>100.9568553216396</v>
+        <v>101.1404338222853</v>
       </c>
       <c r="E72">
-        <v>26.03000000000002</v>
+        <v>27.00900000000001</v>
       </c>
       <c r="F72">
-        <v>68.53000000000002</v>
+        <v>69.50900000000001</v>
       </c>
       <c r="G72">
         <v>9.109999999999999</v>
@@ -7319,28 +7319,28 @@
         <v>19.825</v>
       </c>
       <c r="M72">
-        <v>3.789709000000001</v>
+        <v>3.843847700000001</v>
       </c>
       <c r="N72">
-        <v>16.035291</v>
+        <v>15.9811523</v>
       </c>
       <c r="O72">
-        <v>3.527764019999999</v>
+        <v>3.515853506</v>
       </c>
       <c r="P72">
-        <v>12.50752698</v>
+        <v>12.465298794</v>
       </c>
       <c r="Q72">
-        <v>13.30752698</v>
+        <v>13.265298794</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2006086189396539</v>
+        <v>0.2055303896567376</v>
       </c>
       <c r="T72">
-        <v>2.01767526994329</v>
+        <v>2.08182244164606</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.231272374739061</v>
+        <v>5.157592482137103</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09022895300045386</v>
+        <v>0.09008152031901159</v>
       </c>
       <c r="C73">
-        <v>40.74143382228527</v>
+        <v>39.94668117219265</v>
       </c>
       <c r="D73">
-        <v>101.1404338222853</v>
+        <v>101.3246811721927</v>
       </c>
       <c r="E73">
-        <v>27.009</v>
+        <v>27.988</v>
       </c>
       <c r="F73">
-        <v>69.509</v>
+        <v>70.488</v>
       </c>
       <c r="G73">
         <v>9.109999999999999</v>
@@ -7401,28 +7401,28 @@
         <v>19.825</v>
       </c>
       <c r="M73">
-        <v>3.8438477</v>
+        <v>3.8979864</v>
       </c>
       <c r="N73">
-        <v>15.9811523</v>
+        <v>15.9270136</v>
       </c>
       <c r="O73">
-        <v>3.515853506</v>
+        <v>3.503942992</v>
       </c>
       <c r="P73">
-        <v>12.465298794</v>
+        <v>12.423070608</v>
       </c>
       <c r="Q73">
-        <v>13.265298794</v>
+        <v>13.223070608</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2055303896567374</v>
+        <v>0.2108037154250414</v>
       </c>
       <c r="T73">
-        <v>2.081822441646059</v>
+        <v>2.150551554184742</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.157592482137105</v>
+        <v>5.085959253218533</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09008152031901159</v>
+        <v>0.0899340876375693</v>
       </c>
       <c r="C74">
-        <v>39.94668117219265</v>
+        <v>39.15260103335736</v>
       </c>
       <c r="D74">
-        <v>101.3246811721927</v>
+        <v>101.5096010333574</v>
       </c>
       <c r="E74">
-        <v>27.988</v>
+        <v>28.967</v>
       </c>
       <c r="F74">
-        <v>70.488</v>
+        <v>71.467</v>
       </c>
       <c r="G74">
         <v>9.109999999999999</v>
@@ -7483,28 +7483,28 @@
         <v>19.825</v>
       </c>
       <c r="M74">
-        <v>3.8979864</v>
+        <v>3.9521251</v>
       </c>
       <c r="N74">
-        <v>15.9270136</v>
+        <v>15.8728749</v>
       </c>
       <c r="O74">
-        <v>3.503942992</v>
+        <v>3.492032478</v>
       </c>
       <c r="P74">
-        <v>12.423070608</v>
+        <v>12.380842422</v>
       </c>
       <c r="Q74">
-        <v>13.223070608</v>
+        <v>13.180842422</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2108037154250414</v>
+        <v>0.2164676579169233</v>
       </c>
       <c r="T74">
-        <v>2.150551554184742</v>
+        <v>2.22437171209666</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.085959253218533</v>
+        <v>5.016288578516909</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0899340876375693</v>
+        <v>0.08978665495612703</v>
       </c>
       <c r="C75">
-        <v>39.15260103335736</v>
+        <v>38.35919709455669</v>
       </c>
       <c r="D75">
-        <v>101.5096010333574</v>
+        <v>101.6951970945567</v>
       </c>
       <c r="E75">
-        <v>28.967</v>
+        <v>29.946</v>
       </c>
       <c r="F75">
-        <v>71.467</v>
+        <v>72.446</v>
       </c>
       <c r="G75">
         <v>9.109999999999999</v>
@@ -7565,28 +7565,28 @@
         <v>19.825</v>
       </c>
       <c r="M75">
-        <v>3.9521251</v>
+        <v>4.0062638</v>
       </c>
       <c r="N75">
-        <v>15.8728749</v>
+        <v>15.8187362</v>
       </c>
       <c r="O75">
-        <v>3.492032478</v>
+        <v>3.480121964</v>
       </c>
       <c r="P75">
-        <v>12.380842422</v>
+        <v>12.338614236</v>
       </c>
       <c r="Q75">
-        <v>13.180842422</v>
+        <v>13.138614236</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2164676579169233</v>
+        <v>0.2225672882927962</v>
       </c>
       <c r="T75">
-        <v>2.22437171209666</v>
+        <v>2.30387034369411</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.016288578516909</v>
+        <v>4.948500895023438</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08978665495612703</v>
+        <v>0.08963922227468474</v>
       </c>
       <c r="C76">
-        <v>38.35919709455669</v>
+        <v>37.5664730715952</v>
       </c>
       <c r="D76">
-        <v>101.6951970945567</v>
+        <v>101.8814730715952</v>
       </c>
       <c r="E76">
-        <v>29.946</v>
+        <v>30.92500000000001</v>
       </c>
       <c r="F76">
-        <v>72.446</v>
+        <v>73.42500000000001</v>
       </c>
       <c r="G76">
         <v>9.109999999999999</v>
@@ -7647,28 +7647,28 @@
         <v>19.825</v>
       </c>
       <c r="M76">
-        <v>4.0062638</v>
+        <v>4.0604025</v>
       </c>
       <c r="N76">
-        <v>15.8187362</v>
+        <v>15.7645975</v>
       </c>
       <c r="O76">
-        <v>3.480121964</v>
+        <v>3.46821145</v>
       </c>
       <c r="P76">
-        <v>12.338614236</v>
+        <v>12.29638605</v>
       </c>
       <c r="Q76">
-        <v>13.138614236</v>
+        <v>13.09638605</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2225672882927962</v>
+        <v>0.2291548890987389</v>
       </c>
       <c r="T76">
-        <v>2.30387034369411</v>
+        <v>2.389728865819357</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.948500895023438</v>
+        <v>4.882520883089791</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08963922227468474</v>
+        <v>0.08949178959324246</v>
       </c>
       <c r="C77">
-        <v>37.5664730715952</v>
+        <v>36.77443270755232</v>
       </c>
       <c r="D77">
-        <v>101.8814730715952</v>
+        <v>102.0684327075523</v>
       </c>
       <c r="E77">
-        <v>30.92500000000001</v>
+        <v>31.90400000000001</v>
       </c>
       <c r="F77">
-        <v>73.42500000000001</v>
+        <v>74.40400000000001</v>
       </c>
       <c r="G77">
         <v>9.109999999999999</v>
@@ -7729,28 +7729,28 @@
         <v>19.825</v>
       </c>
       <c r="M77">
-        <v>4.0604025</v>
+        <v>4.114541200000001</v>
       </c>
       <c r="N77">
-        <v>15.7645975</v>
+        <v>15.7104588</v>
       </c>
       <c r="O77">
-        <v>3.46821145</v>
+        <v>3.456300935999999</v>
       </c>
       <c r="P77">
-        <v>12.29638605</v>
+        <v>12.254157864</v>
       </c>
       <c r="Q77">
-        <v>13.09638605</v>
+        <v>13.054157864</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2291548890987389</v>
+        <v>0.2362914566385102</v>
       </c>
       <c r="T77">
-        <v>2.389728865819357</v>
+        <v>2.482742264788374</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.882520883089791</v>
+        <v>4.818277187259662</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08949178959324246</v>
+        <v>0.08934435691180016</v>
       </c>
       <c r="C78">
-        <v>36.77443270755232</v>
+        <v>35.98307977303338</v>
       </c>
       <c r="D78">
-        <v>102.0684327075523</v>
+        <v>102.2560797730334</v>
       </c>
       <c r="E78">
-        <v>31.90400000000001</v>
+        <v>32.88300000000001</v>
       </c>
       <c r="F78">
-        <v>74.40400000000001</v>
+        <v>75.38300000000001</v>
       </c>
       <c r="G78">
         <v>9.109999999999999</v>
@@ -7811,28 +7811,28 @@
         <v>19.825</v>
       </c>
       <c r="M78">
-        <v>4.114541200000001</v>
+        <v>4.168679900000001</v>
       </c>
       <c r="N78">
-        <v>15.7104588</v>
+        <v>15.6563201</v>
       </c>
       <c r="O78">
-        <v>3.456300935999999</v>
+        <v>3.444390422</v>
       </c>
       <c r="P78">
-        <v>12.254157864</v>
+        <v>12.211929678</v>
       </c>
       <c r="Q78">
-        <v>13.054157864</v>
+        <v>13.011929678</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2362914566385102</v>
+        <v>0.2440485952686964</v>
       </c>
       <c r="T78">
-        <v>2.482742264788374</v>
+        <v>2.58384378540687</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.818277187259662</v>
+        <v>4.755702158853692</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08934435691180016</v>
+        <v>0.08919692423035788</v>
       </c>
       <c r="C79">
-        <v>35.98307977303338</v>
+        <v>35.19241806642285</v>
       </c>
       <c r="D79">
-        <v>102.2560797730334</v>
+        <v>102.4444180664229</v>
       </c>
       <c r="E79">
-        <v>32.88300000000001</v>
+        <v>33.86200000000001</v>
       </c>
       <c r="F79">
-        <v>75.38300000000001</v>
+        <v>76.36200000000001</v>
       </c>
       <c r="G79">
         <v>9.109999999999999</v>
@@ -7893,28 +7893,28 @@
         <v>19.825</v>
       </c>
       <c r="M79">
-        <v>4.168679900000001</v>
+        <v>4.222818600000001</v>
       </c>
       <c r="N79">
-        <v>15.6563201</v>
+        <v>15.6021814</v>
       </c>
       <c r="O79">
-        <v>3.444390422</v>
+        <v>3.432479908</v>
       </c>
       <c r="P79">
-        <v>12.211929678</v>
+        <v>12.169701492</v>
       </c>
       <c r="Q79">
-        <v>13.011929678</v>
+        <v>12.969701492</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2440485952686964</v>
+        <v>0.2525109283198086</v>
       </c>
       <c r="T79">
-        <v>2.58384378540687</v>
+        <v>2.694136353354322</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.755702158853692</v>
+        <v>4.694731618355569</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08919692423035788</v>
+        <v>0.08904949154891562</v>
       </c>
       <c r="C80">
-        <v>35.19241806642285</v>
+        <v>34.40245141414076</v>
       </c>
       <c r="D80">
-        <v>102.4444180664229</v>
+        <v>102.6334514141408</v>
       </c>
       <c r="E80">
-        <v>33.86200000000001</v>
+        <v>34.84100000000001</v>
       </c>
       <c r="F80">
-        <v>76.36200000000001</v>
+        <v>77.34100000000001</v>
       </c>
       <c r="G80">
         <v>9.109999999999999</v>
@@ -7975,28 +7975,28 @@
         <v>19.825</v>
       </c>
       <c r="M80">
-        <v>4.222818600000001</v>
+        <v>4.2769573</v>
       </c>
       <c r="N80">
-        <v>15.6021814</v>
+        <v>15.5480427</v>
       </c>
       <c r="O80">
-        <v>3.432479908</v>
+        <v>3.420569394</v>
       </c>
       <c r="P80">
-        <v>12.169701492</v>
+        <v>12.127473306</v>
       </c>
       <c r="Q80">
-        <v>12.969701492</v>
+        <v>12.927473306</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2525109283198086</v>
+        <v>0.2617791978519791</v>
       </c>
       <c r="T80">
-        <v>2.694136353354322</v>
+        <v>2.814932975392006</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.694731618355569</v>
+        <v>4.635304635844739</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08904949154891562</v>
+        <v>0.08890205886747332</v>
       </c>
       <c r="C81">
-        <v>34.40245141414076</v>
+        <v>33.61318367090196</v>
       </c>
       <c r="D81">
-        <v>102.6334514141408</v>
+        <v>102.823183670902</v>
       </c>
       <c r="E81">
-        <v>34.84100000000001</v>
+        <v>35.82000000000001</v>
       </c>
       <c r="F81">
-        <v>77.34100000000001</v>
+        <v>78.32000000000001</v>
       </c>
       <c r="G81">
         <v>9.109999999999999</v>
@@ -8057,28 +8057,28 @@
         <v>19.825</v>
       </c>
       <c r="M81">
-        <v>4.2769573</v>
+        <v>4.331096000000001</v>
       </c>
       <c r="N81">
-        <v>15.5480427</v>
+        <v>15.493904</v>
       </c>
       <c r="O81">
-        <v>3.420569394</v>
+        <v>3.40865888</v>
       </c>
       <c r="P81">
-        <v>12.127473306</v>
+        <v>12.08524512</v>
       </c>
       <c r="Q81">
-        <v>12.927473306</v>
+        <v>12.88524512</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2617791978519791</v>
+        <v>0.2719742943373666</v>
       </c>
       <c r="T81">
-        <v>2.814932975392006</v>
+        <v>2.947809259633459</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.635304635844739</v>
+        <v>4.57736332789668</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08890205886747332</v>
+        <v>0.08875462618603103</v>
       </c>
       <c r="C82">
-        <v>33.61318367090196</v>
+        <v>32.82461871997783</v>
       </c>
       <c r="D82">
-        <v>102.823183670902</v>
+        <v>103.0136187199778</v>
       </c>
       <c r="E82">
-        <v>35.82000000000001</v>
+        <v>36.79900000000001</v>
       </c>
       <c r="F82">
-        <v>78.32000000000001</v>
+        <v>79.29900000000001</v>
       </c>
       <c r="G82">
         <v>9.109999999999999</v>
@@ -8139,28 +8139,28 @@
         <v>19.825</v>
       </c>
       <c r="M82">
-        <v>4.331096000000001</v>
+        <v>4.385234700000001</v>
       </c>
       <c r="N82">
-        <v>15.493904</v>
+        <v>15.4397653</v>
       </c>
       <c r="O82">
-        <v>3.40865888</v>
+        <v>3.396748365999999</v>
       </c>
       <c r="P82">
-        <v>12.08524512</v>
+        <v>12.043016934</v>
       </c>
       <c r="Q82">
-        <v>12.88524512</v>
+        <v>12.843016934</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2719742943373666</v>
+        <v>0.2832425588738476</v>
       </c>
       <c r="T82">
-        <v>2.947809259633459</v>
+        <v>3.094672521163485</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.57736332789668</v>
+        <v>4.520852669527584</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08875462618603103</v>
+        <v>0.09020619350458875</v>
       </c>
       <c r="C83">
-        <v>32.82461871997783</v>
+        <v>30.00083272872304</v>
       </c>
       <c r="D83">
-        <v>103.0136187199778</v>
+        <v>101.168832728723</v>
       </c>
       <c r="E83">
-        <v>36.79900000000001</v>
+        <v>37.77800000000001</v>
       </c>
       <c r="F83">
-        <v>79.29900000000001</v>
+        <v>80.27800000000001</v>
       </c>
       <c r="G83">
         <v>9.109999999999999</v>
@@ -8221,45 +8221,45 @@
         <v>19.825</v>
       </c>
       <c r="M83">
-        <v>4.385234700000001</v>
+        <v>4.640068400000001</v>
       </c>
       <c r="N83">
-        <v>15.4397653</v>
+        <v>15.1849316</v>
       </c>
       <c r="O83">
-        <v>3.396748365999999</v>
+        <v>3.340684952</v>
       </c>
       <c r="P83">
-        <v>12.043016934</v>
+        <v>11.844246648</v>
       </c>
       <c r="Q83">
-        <v>12.843016934</v>
+        <v>12.644246648</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2832425588738476</v>
+        <v>0.2957628528032709</v>
       </c>
       <c r="T83">
-        <v>3.094672521163485</v>
+        <v>3.257853922863515</v>
       </c>
       <c r="U83">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V83">
         <v>0.22</v>
       </c>
       <c r="W83">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>4.520852669527584</v>
+        <v>4.272566326823974</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09020619350458875</v>
+        <v>0.09007826082314649</v>
       </c>
       <c r="C84">
-        <v>30.00083272872304</v>
+        <v>29.18176216514952</v>
       </c>
       <c r="D84">
-        <v>101.168832728723</v>
+        <v>101.3287621651495</v>
       </c>
       <c r="E84">
-        <v>37.77800000000001</v>
+        <v>38.75700000000001</v>
       </c>
       <c r="F84">
-        <v>80.27800000000001</v>
+        <v>81.25700000000001</v>
       </c>
       <c r="G84">
         <v>9.109999999999999</v>
@@ -8303,28 +8303,28 @@
         <v>19.825</v>
       </c>
       <c r="M84">
-        <v>4.640068400000001</v>
+        <v>4.6966546</v>
       </c>
       <c r="N84">
-        <v>15.1849316</v>
+        <v>15.1283454</v>
       </c>
       <c r="O84">
-        <v>3.340684952</v>
+        <v>3.328235988</v>
       </c>
       <c r="P84">
-        <v>11.844246648</v>
+        <v>11.800109412</v>
       </c>
       <c r="Q84">
-        <v>12.644246648</v>
+        <v>12.600109412</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2957628528032709</v>
+        <v>0.309756122489097</v>
       </c>
       <c r="T84">
-        <v>3.257853922863515</v>
+        <v>3.440233136528255</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.272566326823974</v>
+        <v>4.221089624091156</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09007826082314649</v>
+        <v>0.0899503281417042</v>
       </c>
       <c r="C85">
-        <v>29.18176216514952</v>
+        <v>28.36319804058886</v>
       </c>
       <c r="D85">
-        <v>101.3287621651495</v>
+        <v>101.4891980405889</v>
       </c>
       <c r="E85">
-        <v>38.75700000000001</v>
+        <v>39.73600000000002</v>
       </c>
       <c r="F85">
-        <v>81.25700000000001</v>
+        <v>82.23600000000002</v>
       </c>
       <c r="G85">
         <v>9.109999999999999</v>
@@ -8385,28 +8385,28 @@
         <v>19.825</v>
       </c>
       <c r="M85">
-        <v>4.6966546</v>
+        <v>4.753240800000001</v>
       </c>
       <c r="N85">
-        <v>15.1283454</v>
+        <v>15.0717592</v>
       </c>
       <c r="O85">
-        <v>3.328235988</v>
+        <v>3.315787024</v>
       </c>
       <c r="P85">
-        <v>11.800109412</v>
+        <v>11.755972176</v>
       </c>
       <c r="Q85">
-        <v>12.600109412</v>
+        <v>12.555972176</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.309756122489097</v>
+        <v>0.3254985508856513</v>
       </c>
       <c r="T85">
-        <v>3.440233136528255</v>
+        <v>3.645409751901087</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.221089624091156</v>
+        <v>4.170838557137689</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0899503281417042</v>
+        <v>0.08982239546026191</v>
       </c>
       <c r="C86">
-        <v>28.36319804058887</v>
+        <v>27.54514276442123</v>
       </c>
       <c r="D86">
-        <v>101.4891980405889</v>
+        <v>101.6501427644212</v>
       </c>
       <c r="E86">
-        <v>39.736</v>
+        <v>40.715</v>
       </c>
       <c r="F86">
-        <v>82.236</v>
+        <v>83.215</v>
       </c>
       <c r="G86">
         <v>9.109999999999999</v>
@@ -8467,28 +8467,28 @@
         <v>19.825</v>
       </c>
       <c r="M86">
-        <v>4.7532408</v>
+        <v>4.809827</v>
       </c>
       <c r="N86">
-        <v>15.0717592</v>
+        <v>15.015173</v>
       </c>
       <c r="O86">
-        <v>3.315787024</v>
+        <v>3.30333806</v>
       </c>
       <c r="P86">
-        <v>11.755972176</v>
+        <v>11.71183494</v>
       </c>
       <c r="Q86">
-        <v>12.555972176</v>
+        <v>12.51183494</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3254985508856512</v>
+        <v>0.3433399697350794</v>
       </c>
       <c r="T86">
-        <v>3.645409751901084</v>
+        <v>3.877943249323627</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.17083855713769</v>
+        <v>4.121769868230187</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08982239546026191</v>
+        <v>0.08969446277881962</v>
       </c>
       <c r="C87">
-        <v>27.54514276442123</v>
+        <v>26.72759876133453</v>
       </c>
       <c r="D87">
-        <v>101.6501427644212</v>
+        <v>101.8115987613345</v>
       </c>
       <c r="E87">
-        <v>40.715</v>
+        <v>41.694</v>
       </c>
       <c r="F87">
-        <v>83.215</v>
+        <v>84.194</v>
       </c>
       <c r="G87">
         <v>9.109999999999999</v>
@@ -8549,28 +8549,28 @@
         <v>19.825</v>
       </c>
       <c r="M87">
-        <v>4.809827</v>
+        <v>4.8664132</v>
       </c>
       <c r="N87">
-        <v>15.015173</v>
+        <v>14.9585868</v>
       </c>
       <c r="O87">
-        <v>3.30333806</v>
+        <v>3.290889096</v>
       </c>
       <c r="P87">
-        <v>11.71183494</v>
+        <v>11.667697704</v>
       </c>
       <c r="Q87">
-        <v>12.51183494</v>
+        <v>12.467697704</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3433399697350794</v>
+        <v>0.3637301627058544</v>
       </c>
       <c r="T87">
-        <v>3.877943249323627</v>
+        <v>4.143695817806532</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.121769868230187</v>
+        <v>4.07384231162286</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08969446277881962</v>
+        <v>0.08956653009737735</v>
       </c>
       <c r="C88">
-        <v>26.72759876133453</v>
+        <v>25.91056847144618</v>
       </c>
       <c r="D88">
-        <v>101.8115987613345</v>
+        <v>101.9735684714462</v>
       </c>
       <c r="E88">
-        <v>41.694</v>
+        <v>42.673</v>
       </c>
       <c r="F88">
-        <v>84.194</v>
+        <v>85.173</v>
       </c>
       <c r="G88">
         <v>9.109999999999999</v>
@@ -8631,28 +8631,28 @@
         <v>19.825</v>
       </c>
       <c r="M88">
-        <v>4.8664132</v>
+        <v>4.9229994</v>
       </c>
       <c r="N88">
-        <v>14.9585868</v>
+        <v>14.9020006</v>
       </c>
       <c r="O88">
-        <v>3.290889096</v>
+        <v>3.278440132</v>
       </c>
       <c r="P88">
-        <v>11.667697704</v>
+        <v>11.623560468</v>
       </c>
       <c r="Q88">
-        <v>12.467697704</v>
+        <v>12.423560468</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3637301627058544</v>
+        <v>0.3872573084413641</v>
       </c>
       <c r="T88">
-        <v>4.143695817806532</v>
+        <v>4.450333396825269</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.07384231162286</v>
+        <v>4.027016537926045</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08956653009737735</v>
+        <v>0.09184099741593506</v>
       </c>
       <c r="C89">
-        <v>25.91056847144618</v>
+        <v>22.12671968888972</v>
       </c>
       <c r="D89">
-        <v>101.9735684714462</v>
+        <v>99.16871968888972</v>
       </c>
       <c r="E89">
-        <v>42.673</v>
+        <v>43.652</v>
       </c>
       <c r="F89">
-        <v>85.173</v>
+        <v>86.152</v>
       </c>
       <c r="G89">
         <v>9.109999999999999</v>
@@ -8713,45 +8713,45 @@
         <v>19.825</v>
       </c>
       <c r="M89">
-        <v>4.9229994</v>
+        <v>5.2811176</v>
       </c>
       <c r="N89">
-        <v>14.9020006</v>
+        <v>14.5438824</v>
       </c>
       <c r="O89">
-        <v>3.278440132</v>
+        <v>3.199654128</v>
       </c>
       <c r="P89">
-        <v>11.623560468</v>
+        <v>11.344228272</v>
       </c>
       <c r="Q89">
-        <v>12.423560468</v>
+        <v>12.144228272</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3872573084413641</v>
+        <v>0.4147056451327922</v>
       </c>
       <c r="T89">
-        <v>4.450333396825269</v>
+        <v>4.808077239013796</v>
       </c>
       <c r="U89">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V89">
         <v>0.22</v>
       </c>
       <c r="W89">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>4.027016537926045</v>
+        <v>3.753940264462204</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09184099741593506</v>
+        <v>0.09174036473449276</v>
       </c>
       <c r="C90">
-        <v>22.12671968888972</v>
+        <v>21.26855245905979</v>
       </c>
       <c r="D90">
-        <v>99.16871968888972</v>
+        <v>99.28955245905979</v>
       </c>
       <c r="E90">
-        <v>43.652</v>
+        <v>44.631</v>
       </c>
       <c r="F90">
-        <v>86.152</v>
+        <v>87.131</v>
       </c>
       <c r="G90">
         <v>9.109999999999999</v>
@@ -8795,28 +8795,28 @@
         <v>19.825</v>
       </c>
       <c r="M90">
-        <v>5.2811176</v>
+        <v>5.3411303</v>
       </c>
       <c r="N90">
-        <v>14.5438824</v>
+        <v>14.4838697</v>
       </c>
       <c r="O90">
-        <v>3.199654128</v>
+        <v>3.186451334</v>
       </c>
       <c r="P90">
-        <v>11.344228272</v>
+        <v>11.297418366</v>
       </c>
       <c r="Q90">
-        <v>12.144228272</v>
+        <v>12.097418366</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4147056451327922</v>
+        <v>0.4471445884953889</v>
       </c>
       <c r="T90">
-        <v>4.808077239013796</v>
+        <v>5.230865416145691</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.753940264462204</v>
+        <v>3.711761160367123</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09174036473449276</v>
+        <v>0.09163973205305048</v>
       </c>
       <c r="C91">
-        <v>21.26855245905979</v>
+        <v>20.41068004739914</v>
       </c>
       <c r="D91">
-        <v>99.28955245905979</v>
+        <v>99.41068004739915</v>
       </c>
       <c r="E91">
-        <v>44.631</v>
+        <v>45.61000000000001</v>
       </c>
       <c r="F91">
-        <v>87.131</v>
+        <v>88.11000000000001</v>
       </c>
       <c r="G91">
         <v>9.109999999999999</v>
@@ -8877,28 +8877,28 @@
         <v>19.825</v>
       </c>
       <c r="M91">
-        <v>5.3411303</v>
+        <v>5.401143000000001</v>
       </c>
       <c r="N91">
-        <v>14.4838697</v>
+        <v>14.423857</v>
       </c>
       <c r="O91">
-        <v>3.186451334</v>
+        <v>3.173248539999999</v>
       </c>
       <c r="P91">
-        <v>11.297418366</v>
+        <v>11.25060846</v>
       </c>
       <c r="Q91">
-        <v>12.097418366</v>
+        <v>12.05060846</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4471445884953889</v>
+        <v>0.4860713205305049</v>
       </c>
       <c r="T91">
-        <v>5.230865416145691</v>
+        <v>5.738211228703965</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.711761160367123</v>
+        <v>3.670519369696376</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09163973205305048</v>
+        <v>0.0915390993716082</v>
       </c>
       <c r="C92">
-        <v>20.41068004739914</v>
+        <v>19.55310353420973</v>
       </c>
       <c r="D92">
-        <v>99.41068004739915</v>
+        <v>99.53210353420974</v>
       </c>
       <c r="E92">
-        <v>45.61000000000001</v>
+        <v>46.58900000000001</v>
       </c>
       <c r="F92">
-        <v>88.11000000000001</v>
+        <v>89.08900000000001</v>
       </c>
       <c r="G92">
         <v>9.109999999999999</v>
@@ -8959,28 +8959,28 @@
         <v>19.825</v>
       </c>
       <c r="M92">
-        <v>5.401143000000001</v>
+        <v>5.461155700000001</v>
       </c>
       <c r="N92">
-        <v>14.423857</v>
+        <v>14.3638443</v>
       </c>
       <c r="O92">
-        <v>3.173248539999999</v>
+        <v>3.160045746</v>
       </c>
       <c r="P92">
-        <v>11.25060846</v>
+        <v>11.203798554</v>
       </c>
       <c r="Q92">
-        <v>12.05060846</v>
+        <v>12.003798554</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4860713205305049</v>
+        <v>0.5336484374623135</v>
       </c>
       <c r="T92">
-        <v>5.738211228703965</v>
+        <v>6.358300555164079</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.670519369696376</v>
+        <v>3.630183992007405</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0915390993716082</v>
+        <v>0.09143846669016592</v>
       </c>
       <c r="C93">
-        <v>19.55310353420973</v>
+        <v>18.69582400507801</v>
       </c>
       <c r="D93">
-        <v>99.53210353420974</v>
+        <v>99.65382400507802</v>
       </c>
       <c r="E93">
-        <v>46.58900000000001</v>
+        <v>47.56800000000001</v>
       </c>
       <c r="F93">
-        <v>89.08900000000001</v>
+        <v>90.06800000000001</v>
       </c>
       <c r="G93">
         <v>9.109999999999999</v>
@@ -9041,28 +9041,28 @@
         <v>19.825</v>
       </c>
       <c r="M93">
-        <v>5.461155700000001</v>
+        <v>5.521168400000001</v>
       </c>
       <c r="N93">
-        <v>14.3638443</v>
+        <v>14.3038316</v>
       </c>
       <c r="O93">
-        <v>3.160045746</v>
+        <v>3.146842952</v>
       </c>
       <c r="P93">
-        <v>11.203798554</v>
+        <v>11.156988648</v>
       </c>
       <c r="Q93">
-        <v>12.003798554</v>
+        <v>11.956988648</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5336484374623135</v>
+        <v>0.5931198336270743</v>
       </c>
       <c r="T93">
-        <v>6.358300555164079</v>
+        <v>7.133412213239222</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.630183992007405</v>
+        <v>3.590725470355151</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09143846669016592</v>
+        <v>0.09133783400872364</v>
       </c>
       <c r="C94">
-        <v>18.69582400507801</v>
+        <v>17.8388425509073</v>
       </c>
       <c r="D94">
-        <v>99.65382400507802</v>
+        <v>99.77584255090731</v>
       </c>
       <c r="E94">
-        <v>47.56800000000001</v>
+        <v>48.54700000000001</v>
       </c>
       <c r="F94">
-        <v>90.06800000000001</v>
+        <v>91.04700000000001</v>
       </c>
       <c r="G94">
         <v>9.109999999999999</v>
@@ -9123,28 +9123,28 @@
         <v>19.825</v>
       </c>
       <c r="M94">
-        <v>5.521168400000001</v>
+        <v>5.581181100000001</v>
       </c>
       <c r="N94">
-        <v>14.3038316</v>
+        <v>14.2438189</v>
       </c>
       <c r="O94">
-        <v>3.146842952</v>
+        <v>3.133640158</v>
       </c>
       <c r="P94">
-        <v>11.156988648</v>
+        <v>11.110178742</v>
       </c>
       <c r="Q94">
-        <v>11.956988648</v>
+        <v>11.910178742</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5931198336270743</v>
+        <v>0.6695830572674809</v>
       </c>
       <c r="T94">
-        <v>7.133412213239222</v>
+        <v>8.129984345050119</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.590725470355151</v>
+        <v>3.552115519061009</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09133783400872364</v>
+        <v>0.09123720132728136</v>
       </c>
       <c r="C95">
-        <v>17.8388425509073</v>
+        <v>16.98216026795043</v>
       </c>
       <c r="D95">
-        <v>99.77584255090731</v>
+        <v>99.89816026795044</v>
       </c>
       <c r="E95">
-        <v>48.54700000000001</v>
+        <v>49.52600000000001</v>
       </c>
       <c r="F95">
-        <v>91.04700000000001</v>
+        <v>92.02600000000001</v>
       </c>
       <c r="G95">
         <v>9.109999999999999</v>
@@ -9205,28 +9205,28 @@
         <v>19.825</v>
       </c>
       <c r="M95">
-        <v>5.581181100000001</v>
+        <v>5.641193800000001</v>
       </c>
       <c r="N95">
-        <v>14.2438189</v>
+        <v>14.1838062</v>
       </c>
       <c r="O95">
-        <v>3.133640158</v>
+        <v>3.120437364</v>
       </c>
       <c r="P95">
-        <v>11.110178742</v>
+        <v>11.063368836</v>
       </c>
       <c r="Q95">
-        <v>11.910178742</v>
+        <v>11.863368836</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6695830572674809</v>
+        <v>0.7715340221213566</v>
       </c>
       <c r="T95">
-        <v>8.129984345050119</v>
+        <v>9.458747187464649</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.552115519061009</v>
+        <v>3.514327056092275</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09123720132728136</v>
+        <v>0.09321136864583907</v>
       </c>
       <c r="C96">
-        <v>16.98216026795043</v>
+        <v>13.65706658518644</v>
       </c>
       <c r="D96">
-        <v>99.89816026795044</v>
+        <v>97.55206658518645</v>
       </c>
       <c r="E96">
-        <v>49.52600000000001</v>
+        <v>50.50500000000001</v>
       </c>
       <c r="F96">
-        <v>92.02600000000001</v>
+        <v>93.00500000000001</v>
       </c>
       <c r="G96">
         <v>9.109999999999999</v>
@@ -9287,45 +9287,45 @@
         <v>19.825</v>
       </c>
       <c r="M96">
-        <v>5.641193800000001</v>
+        <v>5.961620500000001</v>
       </c>
       <c r="N96">
-        <v>14.1838062</v>
+        <v>13.8633795</v>
       </c>
       <c r="O96">
-        <v>3.120437364</v>
+        <v>3.04994349</v>
       </c>
       <c r="P96">
-        <v>11.063368836</v>
+        <v>10.81343601</v>
       </c>
       <c r="Q96">
-        <v>11.863368836</v>
+        <v>11.61343601</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7715340221213566</v>
+        <v>0.9142653729167826</v>
       </c>
       <c r="T96">
-        <v>9.458747187464649</v>
+        <v>11.31901516684499</v>
       </c>
       <c r="U96">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V96">
         <v>0.22</v>
       </c>
       <c r="W96">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.514327056092275</v>
+        <v>3.325438108648478</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09321136864583907</v>
+        <v>0.09313257596439681</v>
       </c>
       <c r="C97">
-        <v>13.65706658518644</v>
+        <v>12.76959027528096</v>
       </c>
       <c r="D97">
-        <v>97.55206658518645</v>
+        <v>97.64359027528097</v>
       </c>
       <c r="E97">
-        <v>50.50500000000001</v>
+        <v>51.48400000000001</v>
       </c>
       <c r="F97">
-        <v>93.00500000000001</v>
+        <v>93.98400000000001</v>
       </c>
       <c r="G97">
         <v>9.109999999999999</v>
@@ -9369,28 +9369,28 @@
         <v>19.825</v>
       </c>
       <c r="M97">
-        <v>5.961620500000001</v>
+        <v>6.024374400000001</v>
       </c>
       <c r="N97">
-        <v>13.8633795</v>
+        <v>13.8006256</v>
       </c>
       <c r="O97">
-        <v>3.04994349</v>
+        <v>3.036137632</v>
       </c>
       <c r="P97">
-        <v>10.81343601</v>
+        <v>10.764487968</v>
       </c>
       <c r="Q97">
-        <v>11.61343601</v>
+        <v>11.564487968</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9142653729167826</v>
+        <v>1.128362399109922</v>
       </c>
       <c r="T97">
-        <v>11.31901516684499</v>
+        <v>14.10941713591551</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.325438108648478</v>
+        <v>3.290798128350057</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09313257596439679</v>
+        <v>0.09305378328295452</v>
       </c>
       <c r="C98">
-        <v>12.76959027528098</v>
+        <v>11.88228586234224</v>
       </c>
       <c r="D98">
-        <v>97.64359027528099</v>
+        <v>97.73528586234225</v>
       </c>
       <c r="E98">
-        <v>51.48400000000001</v>
+        <v>52.46300000000001</v>
       </c>
       <c r="F98">
-        <v>93.98400000000001</v>
+        <v>94.96300000000001</v>
       </c>
       <c r="G98">
         <v>9.109999999999999</v>
@@ -9451,28 +9451,28 @@
         <v>19.825</v>
       </c>
       <c r="M98">
-        <v>6.024374400000001</v>
+        <v>6.087128300000001</v>
       </c>
       <c r="N98">
-        <v>13.8006256</v>
+        <v>13.7378717</v>
       </c>
       <c r="O98">
-        <v>3.036137632</v>
+        <v>3.022331774</v>
       </c>
       <c r="P98">
-        <v>10.764487968</v>
+        <v>10.715539926</v>
       </c>
       <c r="Q98">
-        <v>11.564487968</v>
+        <v>11.515539926</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.128362399109919</v>
+        <v>1.485190776098483</v>
       </c>
       <c r="T98">
-        <v>14.10941713591547</v>
+        <v>18.76008708436632</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.290798128350057</v>
+        <v>3.256872374449541</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09305378328295452</v>
+        <v>0.09297499060151222</v>
       </c>
       <c r="C99">
-        <v>11.88228586234224</v>
+        <v>10.99515383110278</v>
       </c>
       <c r="D99">
-        <v>97.73528586234225</v>
+        <v>97.82715383110279</v>
       </c>
       <c r="E99">
-        <v>52.46300000000001</v>
+        <v>53.44200000000001</v>
       </c>
       <c r="F99">
-        <v>94.96300000000001</v>
+        <v>95.94200000000001</v>
       </c>
       <c r="G99">
         <v>9.109999999999999</v>
@@ -9533,28 +9533,28 @@
         <v>19.825</v>
       </c>
       <c r="M99">
-        <v>6.087128300000001</v>
+        <v>6.149882200000001</v>
       </c>
       <c r="N99">
-        <v>13.7378717</v>
+        <v>13.6751178</v>
       </c>
       <c r="O99">
-        <v>3.022331774</v>
+        <v>3.008525916</v>
       </c>
       <c r="P99">
-        <v>10.715539926</v>
+        <v>10.666591884</v>
       </c>
       <c r="Q99">
-        <v>11.515539926</v>
+        <v>11.466591884</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.485190776098483</v>
+        <v>2.198847530075609</v>
       </c>
       <c r="T99">
-        <v>18.76008708436632</v>
+        <v>28.06142698126799</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.256872374449541</v>
+        <v>3.223638982873525</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09297499060151222</v>
+        <v>0.09289619792006995</v>
       </c>
       <c r="C100">
-        <v>10.99515383110278</v>
+        <v>10.10819466811938</v>
       </c>
       <c r="D100">
-        <v>97.82715383110279</v>
+        <v>97.91919466811939</v>
       </c>
       <c r="E100">
-        <v>53.44200000000001</v>
+        <v>54.42100000000001</v>
       </c>
       <c r="F100">
-        <v>95.94200000000001</v>
+        <v>96.92100000000001</v>
       </c>
       <c r="G100">
         <v>9.109999999999999</v>
@@ -9615,28 +9615,28 @@
         <v>19.825</v>
       </c>
       <c r="M100">
-        <v>6.149882200000001</v>
+        <v>6.212636100000001</v>
       </c>
       <c r="N100">
-        <v>13.6751178</v>
+        <v>13.6123639</v>
       </c>
       <c r="O100">
-        <v>3.008525916</v>
+        <v>2.994720058</v>
       </c>
       <c r="P100">
-        <v>10.666591884</v>
+        <v>10.617643842</v>
       </c>
       <c r="Q100">
-        <v>11.466591884</v>
+        <v>11.417643842</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.198847530075609</v>
+        <v>4.33981779200699</v>
       </c>
       <c r="T100">
-        <v>28.06142698126799</v>
+        <v>55.96544667197303</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.223638982873525</v>
+        <v>3.19107697294551</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09289619792006995</v>
-      </c>
-      <c r="C101">
-        <v>10.10819466811938</v>
-      </c>
-      <c r="D101">
-        <v>97.91919466811939</v>
-      </c>
-      <c r="E101">
-        <v>54.42100000000001</v>
-      </c>
-      <c r="F101">
-        <v>96.92100000000001</v>
-      </c>
-      <c r="G101">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="H101">
-        <v>55.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>20.625</v>
-      </c>
-      <c r="K101">
-        <v>0.8000000000000007</v>
-      </c>
-      <c r="L101">
-        <v>19.825</v>
-      </c>
-      <c r="M101">
-        <v>6.212636100000001</v>
-      </c>
-      <c r="N101">
-        <v>13.6123639</v>
-      </c>
-      <c r="O101">
-        <v>2.994720058</v>
-      </c>
-      <c r="P101">
-        <v>10.617643842</v>
-      </c>
-      <c r="Q101">
-        <v>11.417643842</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.33981779200699</v>
-      </c>
-      <c r="T101">
-        <v>55.96544667197303</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.04999800000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.19107697294551</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
